--- a/backend/data/atlas/processed/Finra/finra_state.xlsx
+++ b/backend/data/atlas/processed/Finra/finra_state.xlsx
@@ -553,19 +553,19 @@
         <v>2009</v>
       </c>
       <c r="C2">
-        <v>0.213761408586786</v>
+        <v>0.8131377401776678</v>
       </c>
       <c r="D2">
-        <v>0.1597034936892747</v>
+        <v>0.9136830514372416</v>
       </c>
       <c r="E2">
-        <v>0.5848095249365882</v>
+        <v>0.1495797927052838</v>
       </c>
       <c r="F2">
-        <v>0.2917862254043578</v>
+        <v>0.7850832567067783</v>
       </c>
       <c r="G2">
-        <v>0.5253418721185842</v>
+        <v>0.3724140649746276</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -576,19 +576,19 @@
         <v>2009</v>
       </c>
       <c r="C3">
-        <v>0.2093220098678831</v>
+        <v>0.6565763536230874</v>
       </c>
       <c r="D3">
-        <v>0.130213782461916</v>
+        <v>0.570075701661733</v>
       </c>
       <c r="E3">
-        <v>0.6303993834731689</v>
+        <v>0.8921190013026568</v>
       </c>
       <c r="F3">
-        <v>0.2739267611004955</v>
+        <v>0.5092669187960417</v>
       </c>
       <c r="G3">
-        <v>0.4886434361466927</v>
+        <v>0.09907400002174432</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -599,19 +599,19 @@
         <v>2009</v>
       </c>
       <c r="C4">
-        <v>0.2218193495224721</v>
+        <v>0.9279403290977322</v>
       </c>
       <c r="D4">
-        <v>0.1463248174100436</v>
+        <v>0.828882434389815</v>
       </c>
       <c r="E4">
-        <v>0.6117923024510714</v>
+        <v>0.6516240270172476</v>
       </c>
       <c r="F4">
-        <v>0.2560236731990693</v>
+        <v>0.2313731174964812</v>
       </c>
       <c r="G4">
-        <v>0.5462766625641545</v>
+        <v>0.6540699776064821</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -622,19 +622,19 @@
         <v>2009</v>
       </c>
       <c r="C5">
-        <v>0.2004253473094605</v>
+        <v>0.2482161841949743</v>
       </c>
       <c r="D5">
-        <v>0.1498611725594638</v>
+        <v>0.8604013965048312</v>
       </c>
       <c r="E5">
-        <v>0.5703581628242013</v>
+        <v>0.07045014212050314</v>
       </c>
       <c r="F5">
-        <v>0.2576704613570678</v>
+        <v>0.2508784100798958</v>
       </c>
       <c r="G5">
-        <v>0.6145885975406545</v>
+        <v>0.9491469988360339</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -645,19 +645,19 @@
         <v>2009</v>
       </c>
       <c r="C6">
-        <v>0.195152333807727</v>
+        <v>0.1175284836669865</v>
       </c>
       <c r="D6">
-        <v>0.08886204606775906</v>
+        <v>0.07298692197177505</v>
       </c>
       <c r="E6">
-        <v>0.6121185384183766</v>
+        <v>0.6582889576504742</v>
       </c>
       <c r="F6">
-        <v>0.3001373470805664</v>
+        <v>0.8608223410543281</v>
       </c>
       <c r="G6">
-        <v>0.5133882221086147</v>
+        <v>0.2396793802170076</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -668,19 +668,19 @@
         <v>2009</v>
       </c>
       <c r="C7">
-        <v>0.2080683349279012</v>
+        <v>0.5990934137740327</v>
       </c>
       <c r="D7">
-        <v>0.1319962766432815</v>
+        <v>0.607002532857571</v>
       </c>
       <c r="E7">
-        <v>0.6302304464327868</v>
+        <v>0.8910754040067855</v>
       </c>
       <c r="F7">
-        <v>0.2686652699486429</v>
+        <v>0.4159800572707788</v>
       </c>
       <c r="G7">
-        <v>0.4972069923250792</v>
+        <v>0.1306324524161241</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -691,19 +691,19 @@
         <v>2009</v>
       </c>
       <c r="C8">
-        <v>0.2059090597209397</v>
+        <v>0.4928069025021237</v>
       </c>
       <c r="D8">
-        <v>0.1014197865352226</v>
+        <v>0.1227479627611429</v>
       </c>
       <c r="E8">
-        <v>0.6049600864389891</v>
+        <v>0.4999949551157513</v>
       </c>
       <c r="F8">
-        <v>0.2974920688129761</v>
+        <v>0.8405851555216404</v>
       </c>
       <c r="G8">
-        <v>0.5180877716907385</v>
+        <v>0.2866645210558184</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -714,19 +714,19 @@
         <v>2009</v>
       </c>
       <c r="C9">
-        <v>0.225300428132888</v>
+        <v>0.943518742479537</v>
       </c>
       <c r="D9">
-        <v>0.1240134508471565</v>
+        <v>0.4374928968029327</v>
       </c>
       <c r="E9">
-        <v>0.6032892835718053</v>
+        <v>0.4615845189492621</v>
       </c>
       <c r="F9">
-        <v>0.2797208458538112</v>
+        <v>0.6115364694587073</v>
       </c>
       <c r="G9">
-        <v>0.5087303717695227</v>
+        <v>0.2002512109949102</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -737,19 +737,19 @@
         <v>2009</v>
       </c>
       <c r="C10">
-        <v>0.1995561871170052</v>
+        <v>0.2191406254840834</v>
       </c>
       <c r="D10">
-        <v>0.1762235700882631</v>
+        <v>0.9445237591814757</v>
       </c>
       <c r="E10">
-        <v>0.6124711395782361</v>
+        <v>0.6654078343430206</v>
       </c>
       <c r="F10">
-        <v>0.2667510013859146</v>
+        <v>0.3835206352560279</v>
       </c>
       <c r="G10">
-        <v>0.5742318555806093</v>
+        <v>0.8804598394863075</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -760,19 +760,19 @@
         <v>2009</v>
       </c>
       <c r="C11">
-        <v>0.2013804716662259</v>
+        <v>0.2838214700700136</v>
       </c>
       <c r="D11">
-        <v>0.09519904105032721</v>
+        <v>0.09170884723108708</v>
       </c>
       <c r="E11">
-        <v>0.5833442338275647</v>
+        <v>0.136564579815263</v>
       </c>
       <c r="F11">
-        <v>0.3307527862765939</v>
+        <v>0.9521839388442735</v>
       </c>
       <c r="G11">
-        <v>0.4881691103443254</v>
+        <v>0.09770396686444122</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -783,19 +783,19 @@
         <v>2009</v>
       </c>
       <c r="C12">
-        <v>0.2270837972604657</v>
+        <v>0.9481800982260024</v>
       </c>
       <c r="D12">
-        <v>0.1158506344620626</v>
+        <v>0.2816614222125766</v>
       </c>
       <c r="E12">
-        <v>0.608049414464687</v>
+        <v>0.5706510044094152</v>
       </c>
       <c r="F12">
-        <v>0.2803119609996748</v>
+        <v>0.6215520100071155</v>
       </c>
       <c r="G12">
-        <v>0.5275755856260316</v>
+        <v>0.4014781576265476</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -806,19 +806,19 @@
         <v>2009</v>
       </c>
       <c r="C13">
-        <v>0.1955978151934656</v>
+        <v>0.1247704745801335</v>
       </c>
       <c r="D13">
-        <v>0.1138942422680776</v>
+        <v>0.2510457707211282</v>
       </c>
       <c r="E13">
-        <v>0.5868011526151006</v>
+        <v>0.1697909410276041</v>
       </c>
       <c r="F13">
-        <v>0.2942677830042389</v>
+        <v>0.8113216897291236</v>
       </c>
       <c r="G13">
-        <v>0.517868040534421</v>
+        <v>0.2843083921628399</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -829,19 +829,19 @@
         <v>2009</v>
       </c>
       <c r="C14">
-        <v>0.22114893991047</v>
+        <v>0.923521415903531</v>
       </c>
       <c r="D14">
-        <v>0.1066243166983687</v>
+        <v>0.1633451345868793</v>
       </c>
       <c r="E14">
-        <v>0.6125749771563659</v>
+        <v>0.6674870966988835</v>
       </c>
       <c r="F14">
-        <v>0.2525823028282325</v>
+        <v>0.1953102431065468</v>
       </c>
       <c r="G14">
-        <v>0.5068842832828079</v>
+        <v>0.1865455893910181</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -852,19 +852,19 @@
         <v>2009</v>
       </c>
       <c r="C15">
-        <v>0.2129930937019759</v>
+        <v>0.7918359493074244</v>
       </c>
       <c r="D15">
-        <v>0.1345209439784902</v>
+        <v>0.6567264939677495</v>
       </c>
       <c r="E15">
-        <v>0.6376533178936709</v>
+        <v>0.9251221238081431</v>
       </c>
       <c r="F15">
-        <v>0.247099165083045</v>
+        <v>0.1500980749395189</v>
       </c>
       <c r="G15">
-        <v>0.5328867232920546</v>
+        <v>0.4737450012946435</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -875,19 +875,19 @@
         <v>2009</v>
       </c>
       <c r="C16">
-        <v>0.2092925231075217</v>
+        <v>0.6552789779477394</v>
       </c>
       <c r="D16">
-        <v>0.1046337395693172</v>
+        <v>0.1459184284794862</v>
       </c>
       <c r="E16">
-        <v>0.5979512665845823</v>
+        <v>0.3449746139587767</v>
       </c>
       <c r="F16">
-        <v>0.2843782154321108</v>
+        <v>0.6868637635965951</v>
       </c>
       <c r="G16">
-        <v>0.4874739150595963</v>
+        <v>0.0957573716486193</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -898,19 +898,19 @@
         <v>2009</v>
       </c>
       <c r="C17">
-        <v>0.2061208896096101</v>
+        <v>0.5034062259908425</v>
       </c>
       <c r="D17">
-        <v>0.1396302564458033</v>
+        <v>0.7444530213991309</v>
       </c>
       <c r="E17">
-        <v>0.5860859987109558</v>
+        <v>0.1621837103529531</v>
       </c>
       <c r="F17">
-        <v>0.232491438647235</v>
+        <v>0.08379365888800688</v>
       </c>
       <c r="G17">
-        <v>0.5790544355597602</v>
+        <v>0.8982975992233901</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -921,19 +921,19 @@
         <v>2009</v>
       </c>
       <c r="C18">
-        <v>0.1960851737275829</v>
+        <v>0.133375304223712</v>
       </c>
       <c r="D18">
-        <v>0.1213939018244179</v>
+        <v>0.3834399293464312</v>
       </c>
       <c r="E18">
-        <v>0.6086630083802894</v>
+        <v>0.5843956568959707</v>
       </c>
       <c r="F18">
-        <v>0.3230870912000292</v>
+        <v>0.9436554531753096</v>
       </c>
       <c r="G18">
-        <v>0.5739247866436534</v>
+        <v>0.8791669309063209</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -944,19 +944,19 @@
         <v>2009</v>
       </c>
       <c r="C19">
-        <v>0.2085263470935723</v>
+        <v>0.6206085164886137</v>
       </c>
       <c r="D19">
-        <v>0.1379119975278175</v>
+        <v>0.7171185834379046</v>
       </c>
       <c r="E19">
-        <v>0.5954054216285353</v>
+        <v>0.2955749734370269</v>
       </c>
       <c r="F19">
-        <v>0.2443527895768896</v>
+        <v>0.1324222366823466</v>
       </c>
       <c r="G19">
-        <v>0.5281897509974984</v>
+        <v>0.4096379330857308</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -967,19 +967,19 @@
         <v>2009</v>
       </c>
       <c r="C20">
-        <v>0.1972603017403779</v>
+        <v>0.1573340134656108</v>
       </c>
       <c r="D20">
-        <v>0.1371488679548243</v>
+        <v>0.7042494962882506</v>
       </c>
       <c r="E20">
-        <v>0.5685113144514027</v>
+        <v>0.06580914409079215</v>
       </c>
       <c r="F20">
-        <v>0.2650990170390953</v>
+        <v>0.3565439701539158</v>
       </c>
       <c r="G20">
-        <v>0.613062088319468</v>
+        <v>0.9484455371874345</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -990,19 +990,19 @@
         <v>2009</v>
       </c>
       <c r="C21">
-        <v>0.2002747873272357</v>
+        <v>0.2429506806704126</v>
       </c>
       <c r="D21">
-        <v>0.1430048581362359</v>
+        <v>0.7913425554347451</v>
       </c>
       <c r="E21">
-        <v>0.5500307076652829</v>
+        <v>0.04545129997855493</v>
       </c>
       <c r="F21">
-        <v>0.2601612849531096</v>
+        <v>0.2831677289620698</v>
       </c>
       <c r="G21">
-        <v>0.5345747911479121</v>
+        <v>0.4972124619489606</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1013,19 +1013,19 @@
         <v>2009</v>
       </c>
       <c r="C22">
-        <v>0.2114148169858522</v>
+        <v>0.7404172128920872</v>
       </c>
       <c r="D22">
-        <v>0.1328433341188978</v>
+        <v>0.6240690155917271</v>
       </c>
       <c r="E22">
-        <v>0.6111145690322375</v>
+        <v>0.6375481325175277</v>
       </c>
       <c r="F22">
-        <v>0.2746975643971741</v>
+        <v>0.5231130065024897</v>
       </c>
       <c r="G22">
-        <v>0.5520376629520086</v>
+        <v>0.7206074036667254</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1036,19 +1036,19 @@
         <v>2009</v>
       </c>
       <c r="C23">
-        <v>0.1970359464106101</v>
+        <v>0.1523889245340306</v>
       </c>
       <c r="D23">
-        <v>0.120807440965613</v>
+        <v>0.3717611374657721</v>
       </c>
       <c r="E23">
-        <v>0.6117035178576731</v>
+        <v>0.6497974624936664</v>
       </c>
       <c r="F23">
-        <v>0.3151171266134661</v>
+        <v>0.9280438929039813</v>
       </c>
       <c r="G23">
-        <v>0.4686550930278001</v>
+        <v>0.0634045848262193</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1059,19 +1059,19 @@
         <v>2009</v>
       </c>
       <c r="C24">
-        <v>0.2028265748215327</v>
+        <v>0.3445237908771547</v>
       </c>
       <c r="D24">
-        <v>0.07955003897574055</v>
+        <v>0.05886646156111826</v>
       </c>
       <c r="E24">
-        <v>0.6200969977267224</v>
+        <v>0.7941730292418975</v>
       </c>
       <c r="F24">
-        <v>0.2801224780052091</v>
+        <v>0.6183537618431226</v>
       </c>
       <c r="G24">
-        <v>0.5434569568288814</v>
+        <v>0.6182646759544966</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1082,19 +1082,19 @@
         <v>2009</v>
       </c>
       <c r="C25">
-        <v>0.2091014230603482</v>
+        <v>0.6468015143314625</v>
       </c>
       <c r="D25">
-        <v>0.1019064760956864</v>
+        <v>0.1258971793959657</v>
       </c>
       <c r="E25">
-        <v>0.6193654613718071</v>
+        <v>0.7840431357808086</v>
       </c>
       <c r="F25">
-        <v>0.2567098203272881</v>
+        <v>0.2393212651441361</v>
       </c>
       <c r="G25">
-        <v>0.5243097996765541</v>
+        <v>0.3593528292101285</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1105,19 +1105,19 @@
         <v>2009</v>
       </c>
       <c r="C26">
-        <v>0.2025311100242862</v>
+        <v>0.3315095853226121</v>
       </c>
       <c r="D26">
-        <v>0.09826797211662218</v>
+        <v>0.1050633761562875</v>
       </c>
       <c r="E26">
-        <v>0.6551529171310353</v>
+        <v>0.9534262633650656</v>
       </c>
       <c r="F26">
-        <v>0.2736849129339979</v>
+        <v>0.5049207648121606</v>
       </c>
       <c r="G26">
-        <v>0.485706879344772</v>
+        <v>0.0911229235167349</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1128,19 +1128,19 @@
         <v>2009</v>
       </c>
       <c r="C27">
-        <v>0.2153597635055287</v>
+        <v>0.8501776464114613</v>
       </c>
       <c r="D27">
-        <v>0.1710099841341757</v>
+        <v>0.9390740826400151</v>
       </c>
       <c r="E27">
-        <v>0.5719161883011719</v>
+        <v>0.07501406911110436</v>
       </c>
       <c r="F27">
-        <v>0.2589287286081199</v>
+        <v>0.2667731327416659</v>
       </c>
       <c r="G27">
-        <v>0.5788574517909001</v>
+        <v>0.8976535007767332</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1151,19 +1151,19 @@
         <v>2009</v>
       </c>
       <c r="C28">
-        <v>0.2081957981645034</v>
+        <v>0.6051336704962373</v>
       </c>
       <c r="D28">
-        <v>0.1316312846550574</v>
+        <v>0.5995446523363357</v>
       </c>
       <c r="E28">
-        <v>0.6121736796827792</v>
+        <v>0.6594081111536014</v>
       </c>
       <c r="F28">
-        <v>0.2507482765098369</v>
+        <v>0.1785932051474498</v>
       </c>
       <c r="G28">
-        <v>0.579482461449721</v>
+        <v>0.8996742819722456</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1174,19 +1174,19 @@
         <v>2009</v>
       </c>
       <c r="C29">
-        <v>0.2203039161436089</v>
+        <v>0.9170726236774915</v>
       </c>
       <c r="D29">
-        <v>0.1575674957118847</v>
+        <v>0.9054583718812454</v>
       </c>
       <c r="E29">
-        <v>0.6066339262906608</v>
+        <v>0.5384890352719598</v>
       </c>
       <c r="F29">
-        <v>0.216015818570717</v>
+        <v>0.05774922884221696</v>
       </c>
       <c r="G29">
-        <v>0.5511730114849063</v>
+        <v>0.7112555790922258</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1197,19 +1197,19 @@
         <v>2009</v>
       </c>
       <c r="C30">
-        <v>0.2069410217902097</v>
+        <v>0.5442720245230199</v>
       </c>
       <c r="D30">
-        <v>0.1284172872076751</v>
+        <v>0.5318748353046043</v>
       </c>
       <c r="E30">
-        <v>0.6261443866679151</v>
+        <v>0.8608007704079657</v>
       </c>
       <c r="F30">
-        <v>0.2766626993044146</v>
+        <v>0.5582257869394028</v>
       </c>
       <c r="G30">
-        <v>0.5083370901478427</v>
+        <v>0.19724220222662</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1220,19 +1220,19 @@
         <v>2009</v>
       </c>
       <c r="C31">
-        <v>0.2253695239834108</v>
+        <v>0.9437321850087212</v>
       </c>
       <c r="D31">
-        <v>0.1510810647409768</v>
+        <v>0.8694856740331074</v>
       </c>
       <c r="E31">
-        <v>0.6100747710738268</v>
+        <v>0.6153957974644967</v>
       </c>
       <c r="F31">
-        <v>0.2332308335496362</v>
+        <v>0.08582156755161557</v>
       </c>
       <c r="G31">
-        <v>0.5668479156567284</v>
+        <v>0.8432147010912848</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1243,19 +1243,19 @@
         <v>2009</v>
       </c>
       <c r="C32">
-        <v>0.1986547688147682</v>
+        <v>0.1923435812525127</v>
       </c>
       <c r="D32">
-        <v>0.1119013131919326</v>
+        <v>0.2229685466332193</v>
       </c>
       <c r="E32">
-        <v>0.6607770740079001</v>
+        <v>0.9561609788107017</v>
       </c>
       <c r="F32">
-        <v>0.2650755049810667</v>
+        <v>0.3561678535982362</v>
       </c>
       <c r="G32">
-        <v>0.5419427309495131</v>
+        <v>0.5983368355009522</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1266,19 +1266,19 @@
         <v>2009</v>
       </c>
       <c r="C33">
-        <v>0.1770155580382529</v>
+        <v>0.03899828248391756</v>
       </c>
       <c r="D33">
-        <v>0.0783465384685124</v>
+        <v>0.05776220155217633</v>
       </c>
       <c r="E33">
-        <v>0.6034701582469387</v>
+        <v>0.4657254760174968</v>
       </c>
       <c r="F33">
-        <v>0.3447736152279728</v>
+        <v>0.959344197510014</v>
       </c>
       <c r="G33">
-        <v>0.4735431200534456</v>
+        <v>0.06888573131139529</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1289,19 +1289,19 @@
         <v>2009</v>
       </c>
       <c r="C34">
-        <v>0.2197172238954182</v>
+        <v>0.9119406515804984</v>
       </c>
       <c r="D34">
-        <v>0.1493424726029493</v>
+        <v>0.8562757001943146</v>
       </c>
       <c r="E34">
-        <v>0.5944787012047884</v>
+        <v>0.2788973845902865</v>
       </c>
       <c r="F34">
-        <v>0.2863801742140767</v>
+        <v>0.7162698852652819</v>
       </c>
       <c r="G34">
-        <v>0.572818939808192</v>
+        <v>0.8743406991037233</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1312,19 +1312,19 @@
         <v>2009</v>
       </c>
       <c r="C35">
-        <v>0.1787494436400686</v>
+        <v>0.03980109165840266</v>
       </c>
       <c r="D35">
-        <v>0.09445248775773155</v>
+        <v>0.08894487139375362</v>
       </c>
       <c r="E35">
-        <v>0.5795758396454082</v>
+        <v>0.1093840623815921</v>
       </c>
       <c r="F35">
-        <v>0.3525153945944758</v>
+        <v>0.960953787753613</v>
       </c>
       <c r="G35">
-        <v>0.4599052117002094</v>
+        <v>0.05670862642250807</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1335,19 +1335,19 @@
         <v>2009</v>
       </c>
       <c r="C36">
-        <v>0.1932353993378995</v>
+        <v>0.09228955564869423</v>
       </c>
       <c r="D36">
-        <v>0.1293785913400147</v>
+        <v>0.5524072449093594</v>
       </c>
       <c r="E36">
-        <v>0.5724568351788822</v>
+        <v>0.07675299839661484</v>
       </c>
       <c r="F36">
-        <v>0.2727317784858494</v>
+        <v>0.4878048562747507</v>
       </c>
       <c r="G36">
-        <v>0.5396420923714526</v>
+        <v>0.5673246706840405</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1358,19 +1358,19 @@
         <v>2009</v>
       </c>
       <c r="C37">
-        <v>0.1964251005131545</v>
+        <v>0.1398234682882735</v>
       </c>
       <c r="D37">
-        <v>0.1353529068735712</v>
+        <v>0.6722839438104982</v>
       </c>
       <c r="E37">
-        <v>0.6138841503772252</v>
+        <v>0.6929993056355385</v>
       </c>
       <c r="F37">
-        <v>0.2826476639782991</v>
+        <v>0.6599066062876486</v>
       </c>
       <c r="G37">
-        <v>0.5097136095468304</v>
+        <v>0.2079887906190255</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1381,19 +1381,19 @@
         <v>2009</v>
       </c>
       <c r="C38">
-        <v>0.2053154533516649</v>
+        <v>0.4631615287577397</v>
       </c>
       <c r="D38">
-        <v>0.1125592412872896</v>
+        <v>0.2318895671229675</v>
       </c>
       <c r="E38">
-        <v>0.5886711601642104</v>
+        <v>0.1916401313558533</v>
       </c>
       <c r="F38">
-        <v>0.2872806249040333</v>
+        <v>0.7288290346667149</v>
       </c>
       <c r="G38">
-        <v>0.5668705780001088</v>
+        <v>0.8433504107502494</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1404,19 +1404,19 @@
         <v>2009</v>
       </c>
       <c r="C39">
-        <v>0.2190488368574144</v>
+        <v>0.9053538655204436</v>
       </c>
       <c r="D39">
-        <v>0.1775758167268775</v>
+        <v>0.9455586626472008</v>
       </c>
       <c r="E39">
-        <v>0.5909170930881458</v>
+        <v>0.2218282215393961</v>
       </c>
       <c r="F39">
-        <v>0.2304637914663812</v>
+        <v>0.07873750337222069</v>
       </c>
       <c r="G39">
-        <v>0.536104653064485</v>
+        <v>0.5185085612758412</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1427,19 +1427,19 @@
         <v>2009</v>
       </c>
       <c r="C40">
-        <v>0.2066163914098698</v>
+        <v>0.5281510971553156</v>
       </c>
       <c r="D40">
-        <v>0.1075878529084716</v>
+        <v>0.1727203545303259</v>
       </c>
       <c r="E40">
-        <v>0.6041498898429347</v>
+        <v>0.4813337897541591</v>
       </c>
       <c r="F40">
-        <v>0.2642106597590477</v>
+        <v>0.3424969374331687</v>
       </c>
       <c r="G40">
-        <v>0.5941584037607058</v>
+        <v>0.9318999750908832</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1450,19 +1450,19 @@
         <v>2009</v>
       </c>
       <c r="C41">
-        <v>0.1904829021015842</v>
+        <v>0.06886479940175706</v>
       </c>
       <c r="D41">
-        <v>0.1032647998885615</v>
+        <v>0.1353462160564903</v>
       </c>
       <c r="E41">
-        <v>0.5774014346444986</v>
+        <v>0.09719846099627405</v>
       </c>
       <c r="F41">
-        <v>0.3211218722402044</v>
+        <v>0.940590593065134</v>
       </c>
       <c r="G41">
-        <v>0.5540337682160295</v>
+        <v>0.7412809414849864</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1473,19 +1473,19 @@
         <v>2009</v>
       </c>
       <c r="C42">
-        <v>0.2160289237947475</v>
+        <v>0.8630271483125489</v>
       </c>
       <c r="D42">
-        <v>0.1129549873314376</v>
+        <v>0.2374206607464667</v>
       </c>
       <c r="E42">
-        <v>0.6087913715789022</v>
+        <v>0.5872522938650557</v>
       </c>
       <c r="F42">
-        <v>0.2485052965092615</v>
+        <v>0.1603620748928873</v>
       </c>
       <c r="G42">
-        <v>0.5266916721945096</v>
+        <v>0.3898560019002918</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1496,19 +1496,19 @@
         <v>2009</v>
       </c>
       <c r="C43">
-        <v>0.2099074293327472</v>
+        <v>0.6817107242706019</v>
       </c>
       <c r="D43">
-        <v>0.1616110131205293</v>
+        <v>0.919872253544029</v>
       </c>
       <c r="E43">
-        <v>0.6045675745665373</v>
+        <v>0.4909500147623164</v>
       </c>
       <c r="F43">
-        <v>0.2659616077830503</v>
+        <v>0.3704981829875569</v>
       </c>
       <c r="G43">
-        <v>0.5068800079670013</v>
+        <v>0.1865150729527014</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1519,19 +1519,19 @@
         <v>2009</v>
       </c>
       <c r="C44">
-        <v>0.2099785698557247</v>
+        <v>0.6846810618029687</v>
       </c>
       <c r="D44">
-        <v>0.1439868168841071</v>
+        <v>0.8033069701551572</v>
       </c>
       <c r="E44">
-        <v>0.6534474581341226</v>
+        <v>0.9522474405881057</v>
       </c>
       <c r="F44">
-        <v>0.2398086875564661</v>
+        <v>0.1091741894464726</v>
       </c>
       <c r="G44">
-        <v>0.539827114067747</v>
+        <v>0.5698461214802188</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1542,19 +1542,19 @@
         <v>2009</v>
       </c>
       <c r="C45">
-        <v>0.2140558892022796</v>
+        <v>0.8206798457242211</v>
       </c>
       <c r="D45">
-        <v>0.1469371120140678</v>
+        <v>0.8349315144822052</v>
       </c>
       <c r="E45">
-        <v>0.571506697005717</v>
+        <v>0.07375194999736612</v>
       </c>
       <c r="F45">
-        <v>0.245813861433699</v>
+        <v>0.1414509124454139</v>
       </c>
       <c r="G45">
-        <v>0.5712523214381279</v>
+        <v>0.8670291247816231</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1565,19 +1565,19 @@
         <v>2009</v>
       </c>
       <c r="C46">
-        <v>0.2024367220441486</v>
+        <v>0.3274145480221456</v>
       </c>
       <c r="D46">
-        <v>0.1613115483919578</v>
+        <v>0.9189658896331699</v>
       </c>
       <c r="E46">
-        <v>0.5990811402414505</v>
+        <v>0.3684126728661947</v>
       </c>
       <c r="F46">
-        <v>0.2946408420404306</v>
+        <v>0.814980859082123</v>
       </c>
       <c r="G46">
-        <v>0.5202736022914204</v>
+        <v>0.3109207899843462</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1588,19 +1588,19 @@
         <v>2009</v>
       </c>
       <c r="C47">
-        <v>0.2120387823535191</v>
+        <v>0.7619941597417034</v>
       </c>
       <c r="D47">
-        <v>0.150249803921529</v>
+        <v>0.8633880460098089</v>
       </c>
       <c r="E47">
-        <v>0.6326210977829498</v>
+        <v>0.9045264804343893</v>
       </c>
       <c r="F47">
-        <v>0.2442482823427477</v>
+        <v>0.1318076436622027</v>
       </c>
       <c r="G47">
-        <v>0.5402730211654535</v>
+        <v>0.5759050395931147</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1611,19 +1611,19 @@
         <v>2009</v>
       </c>
       <c r="C48">
-        <v>0.2101563142581225</v>
+        <v>0.6920196166006715</v>
       </c>
       <c r="D48">
-        <v>0.1062342431711984</v>
+        <v>0.1597284411964354</v>
       </c>
       <c r="E48">
-        <v>0.6343448394399324</v>
+        <v>0.9126329859553575</v>
       </c>
       <c r="F48">
-        <v>0.2362479389883961</v>
+        <v>0.09525263798341266</v>
       </c>
       <c r="G48">
-        <v>0.5917537674397751</v>
+        <v>0.9282262460187567</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1634,19 +1634,19 @@
         <v>2009</v>
       </c>
       <c r="C49">
-        <v>0.2022717027636641</v>
+        <v>0.3203303242563844</v>
       </c>
       <c r="D49">
-        <v>0.1146037591826907</v>
+        <v>0.261801910725761</v>
       </c>
       <c r="E49">
-        <v>0.6001770412475559</v>
+        <v>0.3918992968175927</v>
       </c>
       <c r="F49">
-        <v>0.3108330717819084</v>
+        <v>0.9152046969384932</v>
       </c>
       <c r="G49">
-        <v>0.4740954893098525</v>
+        <v>0.06960516694756959</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1657,19 +1657,19 @@
         <v>2009</v>
       </c>
       <c r="C50">
-        <v>0.1855929612545295</v>
+        <v>0.0486727722817677</v>
       </c>
       <c r="D50">
-        <v>0.115510627341563</v>
+        <v>0.276126137128446</v>
       </c>
       <c r="E50">
-        <v>0.6336833896023228</v>
+        <v>0.9096661717608765</v>
       </c>
       <c r="F50">
-        <v>0.3215708870734389</v>
+        <v>0.9413295952123</v>
       </c>
       <c r="G50">
-        <v>0.4983314279182394</v>
+        <v>0.1358905435569315</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1680,19 +1680,19 @@
         <v>2009</v>
       </c>
       <c r="C51">
-        <v>0.2060987708378764</v>
+        <v>0.5022996215211313</v>
       </c>
       <c r="D51">
-        <v>0.1381547073788939</v>
+        <v>0.7211188067446878</v>
       </c>
       <c r="E51">
-        <v>0.5669696781518927</v>
+        <v>0.06248878164328795</v>
       </c>
       <c r="F51">
-        <v>0.2486327145305896</v>
+        <v>0.1613353323464575</v>
       </c>
       <c r="G51">
-        <v>0.6097087325733485</v>
+        <v>0.9466609675068536</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1703,19 +1703,19 @@
         <v>2009</v>
       </c>
       <c r="C52">
-        <v>0.1900543149041297</v>
+        <v>0.06621701463588386</v>
       </c>
       <c r="D52">
-        <v>0.09903379503467842</v>
+        <v>0.1089560762950513</v>
       </c>
       <c r="E52">
-        <v>0.6285605751189884</v>
+        <v>0.8799198074331158</v>
       </c>
       <c r="F52">
-        <v>0.3012390685948856</v>
+        <v>0.868331347179247</v>
       </c>
       <c r="G52">
-        <v>0.5364574631317912</v>
+        <v>0.5234131552944645</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1726,19 +1726,19 @@
         <v>2012</v>
       </c>
       <c r="C53">
-        <v>0.2014772867935626</v>
+        <v>0.6528731871983268</v>
       </c>
       <c r="D53">
-        <v>0.1064918941143843</v>
+        <v>0.9441233400554875</v>
       </c>
       <c r="E53">
-        <v>0.553138871013684</v>
+        <v>0.1162928785887345</v>
       </c>
       <c r="F53">
-        <v>0.3773286970246749</v>
+        <v>0.5363432344250004</v>
       </c>
       <c r="G53">
-        <v>0.4997559068393846</v>
+        <v>0.8417234640785323</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1749,19 +1749,19 @@
         <v>2012</v>
       </c>
       <c r="C54">
-        <v>0.1978812082681784</v>
+        <v>0.4994507986212433</v>
       </c>
       <c r="D54">
-        <v>0.08272276727727212</v>
+        <v>0.3680678981758669</v>
       </c>
       <c r="E54">
-        <v>0.6148294029905977</v>
+        <v>0.8735652219044807</v>
       </c>
       <c r="F54">
-        <v>0.3849588330508798</v>
+        <v>0.6415083069717781</v>
       </c>
       <c r="G54">
-        <v>0.4543555490154422</v>
+        <v>0.3453779682969824</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1772,19 +1772,19 @@
         <v>2012</v>
       </c>
       <c r="C55">
-        <v>0.2135968269164389</v>
+        <v>0.9155419504477147</v>
       </c>
       <c r="D55">
-        <v>0.09234495201095945</v>
+        <v>0.7578673786740651</v>
       </c>
       <c r="E55">
-        <v>0.5850256603776374</v>
+        <v>0.5045007045298068</v>
       </c>
       <c r="F55">
-        <v>0.3492475747858416</v>
+        <v>0.1986160127426451</v>
       </c>
       <c r="G55">
-        <v>0.4413592918093185</v>
+        <v>0.2126947289967131</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1795,19 +1795,19 @@
         <v>2012</v>
       </c>
       <c r="C56">
-        <v>0.2192962539509622</v>
+        <v>0.9437401076823322</v>
       </c>
       <c r="D56">
-        <v>0.1084632021993899</v>
+        <v>0.9496818141187661</v>
       </c>
       <c r="E56">
-        <v>0.5400734349584211</v>
+        <v>0.07221556535345046</v>
       </c>
       <c r="F56">
-        <v>0.35891701963656</v>
+        <v>0.2908254599273382</v>
       </c>
       <c r="G56">
-        <v>0.5239271790639377</v>
+        <v>0.919796405917613</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1818,19 +1818,19 @@
         <v>2012</v>
       </c>
       <c r="C57">
-        <v>0.180407720174678</v>
+        <v>0.07217117827088794</v>
       </c>
       <c r="D57">
-        <v>0.08518960751149444</v>
+        <v>0.4739137716530526</v>
       </c>
       <c r="E57">
-        <v>0.5857356026015714</v>
+        <v>0.5171110878801078</v>
       </c>
       <c r="F57">
-        <v>0.472185964932724</v>
+        <v>0.9612181009799073</v>
       </c>
       <c r="G57">
-        <v>0.3670218593734451</v>
+        <v>0.04654665735023359</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1841,19 +1841,19 @@
         <v>2012</v>
       </c>
       <c r="C58">
-        <v>0.2015916934159846</v>
+        <v>0.6573632688461241</v>
       </c>
       <c r="D58">
-        <v>0.08836777927943452</v>
+        <v>0.612669852093542</v>
       </c>
       <c r="E58">
-        <v>0.6267082760172391</v>
+        <v>0.9195187706971937</v>
       </c>
       <c r="F58">
-        <v>0.367373385973967</v>
+        <v>0.3959304600025557</v>
       </c>
       <c r="G58">
-        <v>0.4253773352173471</v>
+        <v>0.1177033207580634</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1864,19 +1864,19 @@
         <v>2012</v>
       </c>
       <c r="C59">
-        <v>0.1990007245058256</v>
+        <v>0.548934435451641</v>
       </c>
       <c r="D59">
-        <v>0.08156669374333084</v>
+        <v>0.3225317837088733</v>
       </c>
       <c r="E59">
-        <v>0.5798876337096267</v>
+        <v>0.4141596653294473</v>
       </c>
       <c r="F59">
-        <v>0.4075485095870942</v>
+        <v>0.8561212493645469</v>
       </c>
       <c r="G59">
-        <v>0.4186837537063931</v>
+        <v>0.09504795725695148</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1887,19 +1887,19 @@
         <v>2012</v>
       </c>
       <c r="C60">
-        <v>0.2110838541411321</v>
+        <v>0.8912127189373631</v>
       </c>
       <c r="D60">
-        <v>0.09158538711041439</v>
+        <v>0.733823416993466</v>
       </c>
       <c r="E60">
-        <v>0.608295642028518</v>
+        <v>0.828540143531223</v>
       </c>
       <c r="F60">
-        <v>0.3914148066343213</v>
+        <v>0.7200458654508513</v>
       </c>
       <c r="G60">
-        <v>0.4309018425915634</v>
+        <v>0.143066604093285</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1910,19 +1910,19 @@
         <v>2012</v>
       </c>
       <c r="C61">
-        <v>0.2062810521079333</v>
+        <v>0.806933703698764</v>
       </c>
       <c r="D61">
-        <v>0.11388972923367</v>
+        <v>0.9578475123650042</v>
       </c>
       <c r="E61">
-        <v>0.63618998631976</v>
+        <v>0.9368669470942023</v>
       </c>
       <c r="F61">
-        <v>0.3427611237279274</v>
+        <v>0.1540370066308234</v>
       </c>
       <c r="G61">
-        <v>0.481134130709534</v>
+        <v>0.6888584164858087</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1933,19 +1933,19 @@
         <v>2012</v>
       </c>
       <c r="C62">
-        <v>0.1890303762470282</v>
+        <v>0.1816394676737656</v>
       </c>
       <c r="D62">
-        <v>0.06002979659170087</v>
+        <v>0.0440039052349324</v>
       </c>
       <c r="E62">
-        <v>0.5891755832829866</v>
+        <v>0.5774583865226321</v>
       </c>
       <c r="F62">
-        <v>0.3886606579186408</v>
+        <v>0.6880563491207258</v>
       </c>
       <c r="G62">
-        <v>0.3690626452908486</v>
+        <v>0.0468525973801688</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1956,19 +1956,19 @@
         <v>2012</v>
       </c>
       <c r="C63">
-        <v>0.1931704759738454</v>
+        <v>0.3039216458938662</v>
       </c>
       <c r="D63">
-        <v>0.08747280224292048</v>
+        <v>0.5746098068688162</v>
       </c>
       <c r="E63">
-        <v>0.5603160903240846</v>
+        <v>0.1624399907851599</v>
       </c>
       <c r="F63">
-        <v>0.4308680548687288</v>
+        <v>0.9350323373731725</v>
       </c>
       <c r="G63">
-        <v>0.50069624703579</v>
+        <v>0.8468051531701789</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1979,19 +1979,19 @@
         <v>2012</v>
       </c>
       <c r="C64">
-        <v>0.2173969191041862</v>
+        <v>0.9372377362549249</v>
       </c>
       <c r="D64">
-        <v>0.08832822409579051</v>
+        <v>0.6110176601063725</v>
       </c>
       <c r="E64">
-        <v>0.5728738253364333</v>
+        <v>0.3023738196701234</v>
       </c>
       <c r="F64">
-        <v>0.4097965078199303</v>
+        <v>0.8685651236019913</v>
       </c>
       <c r="G64">
-        <v>0.4435923040096477</v>
+        <v>0.2317989341798508</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2002,19 +2002,19 @@
         <v>2012</v>
       </c>
       <c r="C65">
-        <v>0.1853136498951752</v>
+        <v>0.1160786161726148</v>
       </c>
       <c r="D65">
-        <v>0.06137014401047166</v>
+        <v>0.04606693530278021</v>
       </c>
       <c r="E65">
-        <v>0.6149008726685348</v>
+        <v>0.87396386909696</v>
       </c>
       <c r="F65">
-        <v>0.3552787983730229</v>
+        <v>0.2523803648677085</v>
       </c>
       <c r="G65">
-        <v>0.4184290393967939</v>
+        <v>0.09433140625038333</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2025,19 +2025,19 @@
         <v>2012</v>
       </c>
       <c r="C66">
-        <v>0.1982830851709921</v>
+        <v>0.5172740607600611</v>
       </c>
       <c r="D66">
-        <v>0.08748874760130244</v>
+        <v>0.5752989494026275</v>
       </c>
       <c r="E66">
-        <v>0.6314803249789881</v>
+        <v>0.9296960668037014</v>
       </c>
       <c r="F66">
-        <v>0.3655343933161997</v>
+        <v>0.3714595611083731</v>
       </c>
       <c r="G66">
-        <v>0.4805812633758545</v>
+        <v>0.6827179908182959</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -2048,19 +2048,19 @@
         <v>2012</v>
       </c>
       <c r="C67">
-        <v>0.19011567027303</v>
+        <v>0.2082673648450852</v>
       </c>
       <c r="D67">
-        <v>0.07960939211079447</v>
+        <v>0.2542065566611362</v>
       </c>
       <c r="E67">
-        <v>0.5638541487009773</v>
+        <v>0.1935438819197924</v>
       </c>
       <c r="F67">
-        <v>0.3911035314836866</v>
+        <v>0.7165527297631071</v>
       </c>
       <c r="G67">
-        <v>0.4172668683717435</v>
+        <v>0.09118120159469245</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2071,19 +2071,19 @@
         <v>2012</v>
       </c>
       <c r="C68">
-        <v>0.2021790199254268</v>
+        <v>0.6798591942657478</v>
       </c>
       <c r="D68">
-        <v>0.08650275556084899</v>
+        <v>0.5321512411152038</v>
       </c>
       <c r="E68">
-        <v>0.5801980753874665</v>
+        <v>0.4194986256532167</v>
       </c>
       <c r="F68">
-        <v>0.3408926071290174</v>
+        <v>0.1434844038724091</v>
       </c>
       <c r="G68">
-        <v>0.531947903834771</v>
+        <v>0.9302988942192627</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -2094,19 +2094,19 @@
         <v>2012</v>
       </c>
       <c r="C69">
-        <v>0.1862634217280889</v>
+        <v>0.1294925071375275</v>
       </c>
       <c r="D69">
-        <v>0.07923469335241907</v>
+        <v>0.242522628400407</v>
       </c>
       <c r="E69">
-        <v>0.6125953443900948</v>
+        <v>0.8601477968887201</v>
       </c>
       <c r="F69">
-        <v>0.3666132227614682</v>
+        <v>0.3857247619374476</v>
       </c>
       <c r="G69">
-        <v>0.4383818774333456</v>
+        <v>0.1896378133303023</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -2117,19 +2117,19 @@
         <v>2012</v>
       </c>
       <c r="C70">
-        <v>0.2082096408029455</v>
+        <v>0.848100660003954</v>
       </c>
       <c r="D70">
-        <v>0.0992632416907183</v>
+        <v>0.8963120749720774</v>
       </c>
       <c r="E70">
-        <v>0.5896490271030529</v>
+        <v>0.5855915154581743</v>
       </c>
       <c r="F70">
-        <v>0.3413551313414467</v>
+        <v>0.1460086535591671</v>
       </c>
       <c r="G70">
-        <v>0.5070008007655816</v>
+        <v>0.8756122120377754</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2140,19 +2140,19 @@
         <v>2012</v>
       </c>
       <c r="C71">
-        <v>0.2063106134010444</v>
+        <v>0.8076501997699529</v>
       </c>
       <c r="D71">
-        <v>0.08443420169821864</v>
+        <v>0.4406598034147725</v>
       </c>
       <c r="E71">
-        <v>0.5450855693213715</v>
+        <v>0.0846736340709513</v>
       </c>
       <c r="F71">
-        <v>0.3503622264657649</v>
+        <v>0.2076223911193435</v>
       </c>
       <c r="G71">
-        <v>0.5038969644042095</v>
+        <v>0.8625186133470257</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2163,19 +2163,19 @@
         <v>2012</v>
       </c>
       <c r="C72">
-        <v>0.2077544576770997</v>
+        <v>0.8393695429577165</v>
       </c>
       <c r="D72">
-        <v>0.08461369047642923</v>
+        <v>0.4485183808254716</v>
       </c>
       <c r="E72">
-        <v>0.5348032811085252</v>
+        <v>0.06310423136116815</v>
       </c>
       <c r="F72">
-        <v>0.35478822360274</v>
+        <v>0.24754149996306</v>
       </c>
       <c r="G72">
-        <v>0.4929592539961679</v>
+        <v>0.7979692296090907</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2186,19 +2186,19 @@
         <v>2012</v>
       </c>
       <c r="C73">
-        <v>0.1937652472569216</v>
+        <v>0.3259892391406021</v>
       </c>
       <c r="D73">
-        <v>0.08184505241618799</v>
+        <v>0.3331786478287622</v>
       </c>
       <c r="E73">
-        <v>0.6022967710624223</v>
+        <v>0.7696027318147962</v>
       </c>
       <c r="F73">
-        <v>0.3258812794823763</v>
+        <v>0.08692215131870135</v>
       </c>
       <c r="G73">
-        <v>0.5110827760482389</v>
+        <v>0.8900282481372375</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2209,19 +2209,19 @@
         <v>2012</v>
       </c>
       <c r="C74">
-        <v>0.1852663355124052</v>
+        <v>0.1154620062357108</v>
       </c>
       <c r="D74">
-        <v>0.08184923616280149</v>
+        <v>0.3333402863661186</v>
       </c>
       <c r="E74">
-        <v>0.6047346994046608</v>
+        <v>0.795793555342009</v>
       </c>
       <c r="F74">
-        <v>0.4306726617472277</v>
+        <v>0.9347041889547674</v>
       </c>
       <c r="G74">
-        <v>0.4424622861313633</v>
+        <v>0.2219348193962387</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2232,19 +2232,19 @@
         <v>2012</v>
       </c>
       <c r="C75">
-        <v>0.1742426498220055</v>
+        <v>0.05059194938510694</v>
       </c>
       <c r="D75">
-        <v>0.06423390234239798</v>
+        <v>0.05254484359986723</v>
       </c>
       <c r="E75">
-        <v>0.6010923489128456</v>
+        <v>0.7554911156439017</v>
       </c>
       <c r="F75">
-        <v>0.4620739850789243</v>
+        <v>0.9592326424054256</v>
       </c>
       <c r="G75">
-        <v>0.4305976266652943</v>
+        <v>0.1414869669161415</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2255,19 +2255,19 @@
         <v>2012</v>
       </c>
       <c r="C76">
-        <v>0.2048441444161885</v>
+        <v>0.7686899198514862</v>
       </c>
       <c r="D76">
-        <v>0.0823121225069456</v>
+        <v>0.3515072096636588</v>
       </c>
       <c r="E76">
-        <v>0.575262456667995</v>
+        <v>0.338202790961305</v>
       </c>
       <c r="F76">
-        <v>0.3962960667400035</v>
+        <v>0.7705213385748469</v>
       </c>
       <c r="G76">
-        <v>0.4775152552548027</v>
+        <v>0.6471548812600272</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2278,19 +2278,19 @@
         <v>2012</v>
       </c>
       <c r="C77">
-        <v>0.187634311323525</v>
+        <v>0.1526924224169</v>
       </c>
       <c r="D77">
-        <v>0.07190585999537363</v>
+        <v>0.09869373580843321</v>
       </c>
       <c r="E77">
-        <v>0.6036154898976069</v>
+        <v>0.7841612826042363</v>
       </c>
       <c r="F77">
-        <v>0.3931935783345015</v>
+        <v>0.7393858666895322</v>
       </c>
       <c r="G77">
-        <v>0.4418330010406052</v>
+        <v>0.2166163119530022</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2301,19 +2301,19 @@
         <v>2012</v>
       </c>
       <c r="C78">
-        <v>0.229952681041581</v>
+        <v>0.9571523170666815</v>
       </c>
       <c r="D78">
-        <v>0.09198191383624234</v>
+        <v>0.74661169964004</v>
       </c>
       <c r="E78">
-        <v>0.5057192265468949</v>
+        <v>0.04628831177644759</v>
       </c>
       <c r="F78">
-        <v>0.3011270339922633</v>
+        <v>0.0538184326315947</v>
       </c>
       <c r="G78">
-        <v>0.492726008952784</v>
+        <v>0.7962336570280895</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2324,19 +2324,19 @@
         <v>2012</v>
       </c>
       <c r="C79">
-        <v>0.202311422707469</v>
+        <v>0.6847965751354974</v>
       </c>
       <c r="D79">
-        <v>0.09438442199293123</v>
+        <v>0.8130462714621537</v>
       </c>
       <c r="E79">
-        <v>0.5858014840517318</v>
+        <v>0.5182801458590468</v>
       </c>
       <c r="F79">
-        <v>0.3604495571144831</v>
+        <v>0.3083335502264569</v>
       </c>
       <c r="G79">
-        <v>0.486701414267354</v>
+        <v>0.7456215808770592</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2347,19 +2347,19 @@
         <v>2012</v>
       </c>
       <c r="C80">
-        <v>0.2031071386722457</v>
+        <v>0.7133637386507277</v>
       </c>
       <c r="D80">
-        <v>0.08545896544318525</v>
+        <v>0.4858542561972194</v>
       </c>
       <c r="E80">
-        <v>0.6383786908923591</v>
+        <v>0.939455470559757</v>
       </c>
       <c r="F80">
-        <v>0.34283147984234</v>
+        <v>0.1544530946839521</v>
       </c>
       <c r="G80">
-        <v>0.5187930983904122</v>
+        <v>0.910241819511786</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2370,19 +2370,19 @@
         <v>2012</v>
       </c>
       <c r="C81">
-        <v>0.1996749630701202</v>
+        <v>0.5782575145886357</v>
       </c>
       <c r="D81">
-        <v>0.0802501593515197</v>
+        <v>0.2752515634363287</v>
       </c>
       <c r="E81">
-        <v>0.6066429150177359</v>
+        <v>0.814129571765255</v>
       </c>
       <c r="F81">
-        <v>0.3926509981961964</v>
+        <v>0.7335998132863505</v>
       </c>
       <c r="G81">
-        <v>0.4303151171933045</v>
+        <v>0.1400402848395959</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2393,19 +2393,19 @@
         <v>2012</v>
       </c>
       <c r="C82">
-        <v>0.2159685851259911</v>
+        <v>0.9307000639685461</v>
       </c>
       <c r="D82">
-        <v>0.1042893182276325</v>
+        <v>0.9351714039966582</v>
       </c>
       <c r="E82">
-        <v>0.5835233816988188</v>
+        <v>0.4778097025010037</v>
       </c>
       <c r="F82">
-        <v>0.3166203572623572</v>
+        <v>0.06904018267447203</v>
       </c>
       <c r="G82">
-        <v>0.4832493486632889</v>
+        <v>0.7115313325793505</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2416,19 +2416,19 @@
         <v>2012</v>
       </c>
       <c r="C83">
-        <v>0.1909805269090356</v>
+        <v>0.2322294364201891</v>
       </c>
       <c r="D83">
-        <v>0.08554866215131693</v>
+        <v>0.4898352883076962</v>
       </c>
       <c r="E83">
-        <v>0.6237319756168531</v>
+        <v>0.911219572275161</v>
       </c>
       <c r="F83">
-        <v>0.3741030484690291</v>
+        <v>0.4901778325990442</v>
       </c>
       <c r="G83">
-        <v>0.5025242427632254</v>
+        <v>0.8560697761195268</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2439,19 +2439,19 @@
         <v>2012</v>
       </c>
       <c r="C84">
-        <v>0.1792042772883984</v>
+        <v>0.06594896227639999</v>
       </c>
       <c r="D84">
-        <v>0.05811108974423419</v>
+        <v>0.04180783878952051</v>
       </c>
       <c r="E84">
-        <v>0.5639530234799721</v>
+        <v>0.1945028911696057</v>
       </c>
       <c r="F84">
-        <v>0.4134083410297065</v>
+        <v>0.8858364084705193</v>
       </c>
       <c r="G84">
-        <v>0.4376562860418348</v>
+        <v>0.184427151889809</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2462,19 +2462,19 @@
         <v>2012</v>
       </c>
       <c r="C85">
-        <v>0.2015065197719339</v>
+        <v>0.6540237069764483</v>
       </c>
       <c r="D85">
-        <v>0.08059477554345215</v>
+        <v>0.287114930648076</v>
       </c>
       <c r="E85">
-        <v>0.5757830351323547</v>
+        <v>0.3463528002536084</v>
       </c>
       <c r="F85">
-        <v>0.3457816347888935</v>
+        <v>0.173189820994289</v>
       </c>
       <c r="G85">
-        <v>0.5102270310910431</v>
+        <v>0.8872472086910733</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2485,19 +2485,19 @@
         <v>2012</v>
       </c>
       <c r="C86">
-        <v>0.1909300749752498</v>
+        <v>0.2307635116787827</v>
       </c>
       <c r="D86">
-        <v>0.10084106578947</v>
+        <v>0.9121915940986691</v>
       </c>
       <c r="E86">
-        <v>0.544186219472184</v>
+        <v>0.08210527085983294</v>
       </c>
       <c r="F86">
-        <v>0.4577281539078968</v>
+        <v>0.9579027854617138</v>
       </c>
       <c r="G86">
-        <v>0.3978724664492568</v>
+        <v>0.05957723739771036</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2508,19 +2508,19 @@
         <v>2012</v>
       </c>
       <c r="C87">
-        <v>0.2169119289020691</v>
+        <v>0.9351982586892493</v>
       </c>
       <c r="D87">
-        <v>0.09140363389402208</v>
+        <v>0.7277909468977581</v>
       </c>
       <c r="E87">
-        <v>0.5679730635867839</v>
+        <v>0.2378562881420863</v>
       </c>
       <c r="F87">
-        <v>0.3626277655360011</v>
+        <v>0.334477217790799</v>
       </c>
       <c r="G87">
-        <v>0.4222098041006136</v>
+        <v>0.1060104341600571</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2531,19 +2531,19 @@
         <v>2012</v>
       </c>
       <c r="C88">
-        <v>0.1672880038262934</v>
+        <v>0.04313652356322422</v>
       </c>
       <c r="D88">
-        <v>0.08492828270842279</v>
+        <v>0.4623618852818275</v>
       </c>
       <c r="E88">
-        <v>0.6013910620709869</v>
+        <v>0.759063765101746</v>
       </c>
       <c r="F88">
-        <v>0.4214188964055916</v>
+        <v>0.9142226206872557</v>
       </c>
       <c r="G88">
-        <v>0.4708763221975991</v>
+        <v>0.5629326416854883</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2554,19 +2554,19 @@
         <v>2012</v>
       </c>
       <c r="C89">
-        <v>0.1973502135952736</v>
+        <v>0.4759113516676761</v>
       </c>
       <c r="D89">
-        <v>0.07969194939665429</v>
+        <v>0.2568429945242401</v>
       </c>
       <c r="E89">
-        <v>0.5420053337138259</v>
+        <v>0.07650699794095277</v>
       </c>
       <c r="F89">
-        <v>0.3456267627932941</v>
+        <v>0.1721418007497943</v>
       </c>
       <c r="G89">
-        <v>0.4943359208742187</v>
+        <v>0.8078842756433808</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2577,19 +2577,19 @@
         <v>2012</v>
       </c>
       <c r="C90">
-        <v>0.1924842210382274</v>
+        <v>0.2797896593116352</v>
       </c>
       <c r="D90">
-        <v>0.1090927260782651</v>
+        <v>0.9510865239150038</v>
       </c>
       <c r="E90">
-        <v>0.5749508373860664</v>
+        <v>0.3333801471948537</v>
       </c>
       <c r="F90">
-        <v>0.374456603524217</v>
+        <v>0.4952393412204664</v>
       </c>
       <c r="G90">
-        <v>0.4701418213509581</v>
+        <v>0.5531764146110296</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2600,19 +2600,19 @@
         <v>2012</v>
       </c>
       <c r="C91">
-        <v>0.1947746167949458</v>
+        <v>0.365657809636975</v>
       </c>
       <c r="D91">
-        <v>0.07218940523150669</v>
+        <v>0.1018133666166509</v>
       </c>
       <c r="E91">
-        <v>0.5886314211844975</v>
+        <v>0.5680453970933238</v>
       </c>
       <c r="F91">
-        <v>0.3629057418077892</v>
+        <v>0.3379147390479832</v>
       </c>
       <c r="G91">
-        <v>0.5111421268163774</v>
+        <v>0.8902166672582098</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2623,19 +2623,19 @@
         <v>2012</v>
       </c>
       <c r="C92">
-        <v>0.1841706135278079</v>
+        <v>0.1024311227235105</v>
       </c>
       <c r="D92">
-        <v>0.06693232172265096</v>
+        <v>0.06248626807182786</v>
       </c>
       <c r="E92">
-        <v>0.5654947247741143</v>
+        <v>0.2101142643123489</v>
       </c>
       <c r="F92">
-        <v>0.3868273874421218</v>
+        <v>0.6654767206769063</v>
       </c>
       <c r="G92">
-        <v>0.4950238948350967</v>
+        <v>0.8126315638022084</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2646,19 +2646,19 @@
         <v>2012</v>
       </c>
       <c r="C93">
-        <v>0.1980664618371603</v>
+        <v>0.5076699716955725</v>
       </c>
       <c r="D93">
-        <v>0.06431063144859252</v>
+        <v>0.05276757220977626</v>
       </c>
       <c r="E93">
-        <v>0.5666123857464067</v>
+        <v>0.2222171222713407</v>
       </c>
       <c r="F93">
-        <v>0.3542068515976806</v>
+        <v>0.2419143535218056</v>
       </c>
       <c r="G93">
-        <v>0.4719759884881372</v>
+        <v>0.5774142368522831</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2669,19 +2669,19 @@
         <v>2012</v>
       </c>
       <c r="C94">
-        <v>0.1958270940846615</v>
+        <v>0.4095046392285143</v>
       </c>
       <c r="D94">
-        <v>0.09380863138367099</v>
+        <v>0.7988372988018086</v>
       </c>
       <c r="E94">
-        <v>0.5496252539477623</v>
+        <v>0.1003703905069916</v>
       </c>
       <c r="F94">
-        <v>0.3546964122836558</v>
+        <v>0.2466451077893542</v>
       </c>
       <c r="G94">
-        <v>0.450039219606055</v>
+        <v>0.2957355791267752</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2692,19 +2692,19 @@
         <v>2012</v>
       </c>
       <c r="C95">
-        <v>0.1769863420526092</v>
+        <v>0.05741148685410102</v>
       </c>
       <c r="D95">
-        <v>0.09253142547273933</v>
+        <v>0.7634796199925052</v>
       </c>
       <c r="E95">
-        <v>0.6106772177983587</v>
+        <v>0.8470453624838665</v>
       </c>
       <c r="F95">
-        <v>0.3863944255331971</v>
+        <v>0.6600049598972795</v>
       </c>
       <c r="G95">
-        <v>0.4645930432087163</v>
+        <v>0.4783093379951391</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2715,19 +2715,19 @@
         <v>2012</v>
       </c>
       <c r="C96">
-        <v>0.2053808686935365</v>
+        <v>0.7837671804214599</v>
       </c>
       <c r="D96">
-        <v>0.10058475901672</v>
+        <v>0.9098865547842404</v>
       </c>
       <c r="E96">
-        <v>0.5590687216178241</v>
+        <v>0.1528922403142184</v>
       </c>
       <c r="F96">
-        <v>0.3985286105482721</v>
+        <v>0.7908551126135405</v>
       </c>
       <c r="G96">
-        <v>0.4962678093012969</v>
+        <v>0.8208718066557552</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2738,19 +2738,19 @@
         <v>2012</v>
       </c>
       <c r="C97">
-        <v>0.2087436165584529</v>
+        <v>0.857622102405964</v>
       </c>
       <c r="D97">
-        <v>0.1039150845493022</v>
+        <v>0.9332813672390617</v>
       </c>
       <c r="E97">
-        <v>0.5459697492145189</v>
+        <v>0.08735973445201051</v>
       </c>
       <c r="F97">
-        <v>0.4320138766561172</v>
+        <v>0.9368853838234912</v>
       </c>
       <c r="G97">
-        <v>0.4314895184644134</v>
+        <v>0.1461829719031911</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2761,19 +2761,19 @@
         <v>2012</v>
       </c>
       <c r="C98">
-        <v>0.1839500742256381</v>
+        <v>0.1000799824154438</v>
       </c>
       <c r="D98">
-        <v>0.09534105958940316</v>
+        <v>0.8343768278818434</v>
       </c>
       <c r="E98">
-        <v>0.6454000666701959</v>
+        <v>0.9454293283627407</v>
       </c>
       <c r="F98">
-        <v>0.4190556289984053</v>
+        <v>0.9070808705870467</v>
       </c>
       <c r="G98">
-        <v>0.4505644282100207</v>
+        <v>0.301501128233929</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2784,19 +2784,19 @@
         <v>2012</v>
       </c>
       <c r="C99">
-        <v>0.2113207252695728</v>
+        <v>0.8939633714623882</v>
       </c>
       <c r="D99">
-        <v>0.07945155375631203</v>
+        <v>0.2492283815730164</v>
       </c>
       <c r="E99">
-        <v>0.6025670121629261</v>
+        <v>0.7726619272493817</v>
       </c>
       <c r="F99">
-        <v>0.2997116015162498</v>
+        <v>0.05299243191658695</v>
       </c>
       <c r="G99">
-        <v>0.5029601481853562</v>
+        <v>0.8581635771361353</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2807,19 +2807,19 @@
         <v>2012</v>
       </c>
       <c r="C100">
-        <v>0.1933465351210609</v>
+        <v>0.3103457249572128</v>
       </c>
       <c r="D100">
-        <v>0.08391024650128692</v>
+        <v>0.4179330678384319</v>
       </c>
       <c r="E100">
-        <v>0.5929566146246441</v>
+        <v>0.640533219498715</v>
       </c>
       <c r="F100">
-        <v>0.3870309264873171</v>
+        <v>0.6680312055318642</v>
       </c>
       <c r="G100">
-        <v>0.4371165213558952</v>
+        <v>0.1806522653916149</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2830,19 +2830,19 @@
         <v>2012</v>
       </c>
       <c r="C101">
-        <v>0.2026780070786093</v>
+        <v>0.6981970425471514</v>
       </c>
       <c r="D101">
-        <v>0.08270126085985764</v>
+        <v>0.3671908448084973</v>
       </c>
       <c r="E101">
-        <v>0.6061795520577763</v>
+        <v>0.8098474815665474</v>
       </c>
       <c r="F101">
-        <v>0.3654152972993545</v>
+        <v>0.3699014433468986</v>
       </c>
       <c r="G101">
-        <v>0.4657694339828209</v>
+        <v>0.4942482481526315</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2853,19 +2853,19 @@
         <v>2012</v>
       </c>
       <c r="C102">
-        <v>0.1975570858291234</v>
+        <v>0.4850740348233319</v>
       </c>
       <c r="D102">
-        <v>0.08470725326437749</v>
+        <v>0.4526270453663178</v>
       </c>
       <c r="E102">
-        <v>0.5548416937365451</v>
+        <v>0.125437702930386</v>
       </c>
       <c r="F102">
-        <v>0.3184130068957644</v>
+        <v>0.07182455413342215</v>
       </c>
       <c r="G102">
-        <v>0.5034171179339334</v>
+        <v>0.8603123437960405</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -2876,19 +2876,19 @@
         <v>2012</v>
       </c>
       <c r="C103">
-        <v>0.1908088490419271</v>
+        <v>0.2272757916669598</v>
       </c>
       <c r="D103">
-        <v>0.07446448525718552</v>
+        <v>0.1327388936713549</v>
       </c>
       <c r="E103">
-        <v>0.5973831409182435</v>
+        <v>0.7071677011996761</v>
       </c>
       <c r="F103">
-        <v>0.3459058464085171</v>
+        <v>0.174035666580804</v>
       </c>
       <c r="G103">
-        <v>0.46933788815799</v>
+        <v>0.5424334971144007</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -2899,19 +2899,19 @@
         <v>2015</v>
       </c>
       <c r="C104">
-        <v>0.2204681131919822</v>
+        <v>0.8446123710555022</v>
       </c>
       <c r="D104">
-        <v>0.1031612017971706</v>
+        <v>0.7096973427996045</v>
       </c>
       <c r="E104">
-        <v>0.4969517157593457</v>
+        <v>0.1083060644986157</v>
       </c>
       <c r="F104">
-        <v>0.4352127972655628</v>
+        <v>0.2042586276061192</v>
       </c>
       <c r="G104">
-        <v>0.4279988644938456</v>
+        <v>0.7728317284883375</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -2922,19 +2922,19 @@
         <v>2015</v>
       </c>
       <c r="C105">
-        <v>0.2171486488774835</v>
+        <v>0.7933118946618714</v>
       </c>
       <c r="D105">
-        <v>0.1125414853812342</v>
+        <v>0.9065462798306612</v>
       </c>
       <c r="E105">
-        <v>0.56120179017341</v>
+        <v>0.7750288510218362</v>
       </c>
       <c r="F105">
-        <v>0.4683368355398739</v>
+        <v>0.5816411428338607</v>
       </c>
       <c r="G105">
-        <v>0.3482088589358064</v>
+        <v>0.07084024948118746</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -2945,19 +2945,19 @@
         <v>2015</v>
       </c>
       <c r="C106">
-        <v>0.2212763719638113</v>
+        <v>0.8547009026594097</v>
       </c>
       <c r="D106">
-        <v>0.10177974293301</v>
+        <v>0.6587956201583193</v>
       </c>
       <c r="E106">
-        <v>0.5424734173086446</v>
+        <v>0.5466890056648648</v>
       </c>
       <c r="F106">
-        <v>0.4282422514642224</v>
+        <v>0.1589093284867414</v>
       </c>
       <c r="G106">
-        <v>0.4083269637895702</v>
+        <v>0.5355572744851126</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -2968,19 +2968,19 @@
         <v>2015</v>
       </c>
       <c r="C107">
-        <v>0.2285106733631451</v>
+        <v>0.9137390731038763</v>
       </c>
       <c r="D107">
-        <v>0.1245977120782253</v>
+        <v>0.957351695981809</v>
       </c>
       <c r="E107">
-        <v>0.509829649271162</v>
+        <v>0.170292239898498</v>
       </c>
       <c r="F107">
-        <v>0.4861527113369354</v>
+        <v>0.7737389429663322</v>
       </c>
       <c r="G107">
-        <v>0.4561021917690348</v>
+        <v>0.9145289595927764</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -2991,19 +2991,19 @@
         <v>2015</v>
       </c>
       <c r="C108">
-        <v>0.1979406647026294</v>
+        <v>0.2689586087782511</v>
       </c>
       <c r="D108">
-        <v>0.09762556260206391</v>
+        <v>0.482746039175843</v>
       </c>
       <c r="E108">
-        <v>0.494367624005919</v>
+        <v>0.1001909657410537</v>
       </c>
       <c r="F108">
-        <v>0.5787535133045049</v>
+        <v>0.9505224156253199</v>
       </c>
       <c r="G108">
-        <v>0.3351446567091555</v>
+        <v>0.05748528385234492</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -3014,19 +3014,19 @@
         <v>2015</v>
       </c>
       <c r="C109">
-        <v>0.2119847739293584</v>
+        <v>0.678193671537838</v>
       </c>
       <c r="D109">
-        <v>0.1027674059986717</v>
+        <v>0.6957441317099536</v>
       </c>
       <c r="E109">
-        <v>0.5221572749560313</v>
+        <v>0.2762509003451638</v>
       </c>
       <c r="F109">
-        <v>0.4678910803411652</v>
+        <v>0.5759327127699475</v>
       </c>
       <c r="G109">
-        <v>0.3765321642008831</v>
+        <v>0.1705677906312122</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -3037,19 +3037,19 @@
         <v>2015</v>
       </c>
       <c r="C110">
-        <v>0.1966159880456424</v>
+        <v>0.2390836915258816</v>
       </c>
       <c r="D110">
-        <v>0.08457018600338281</v>
+        <v>0.1021530260612584</v>
       </c>
       <c r="E110">
-        <v>0.5531987111854613</v>
+        <v>0.6900617325250981</v>
       </c>
       <c r="F110">
-        <v>0.4861231894703093</v>
+        <v>0.7734935442443986</v>
       </c>
       <c r="G110">
-        <v>0.3800766238088008</v>
+        <v>0.1962247326416264</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -3060,19 +3060,19 @@
         <v>2015</v>
       </c>
       <c r="C111">
-        <v>0.2178317564702621</v>
+        <v>0.805252839156828</v>
       </c>
       <c r="D111">
-        <v>0.1106033941804918</v>
+        <v>0.8841647072228616</v>
       </c>
       <c r="E111">
-        <v>0.5589466216158109</v>
+        <v>0.7533751387178453</v>
       </c>
       <c r="F111">
-        <v>0.4150143037174149</v>
+        <v>0.103774416267416</v>
       </c>
       <c r="G111">
-        <v>0.3694337141113407</v>
+        <v>0.1304253454532587</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -3083,19 +3083,19 @@
         <v>2015</v>
       </c>
       <c r="C112">
-        <v>0.1958211516548526</v>
+        <v>0.2225759616953633</v>
       </c>
       <c r="D112">
-        <v>0.1040439674928308</v>
+        <v>0.7392471566925005</v>
       </c>
       <c r="E112">
-        <v>0.5996538429664243</v>
+        <v>0.9357404412843642</v>
       </c>
       <c r="F112">
-        <v>0.4841144803086764</v>
+        <v>0.7561845904632907</v>
       </c>
       <c r="G112">
-        <v>0.4301416385063438</v>
+        <v>0.7913407652012645</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -3106,19 +3106,19 @@
         <v>2015</v>
       </c>
       <c r="C113">
-        <v>0.1964047142650436</v>
+        <v>0.2345916441153986</v>
       </c>
       <c r="D113">
-        <v>0.07244387930558562</v>
+        <v>0.04101463528786225</v>
       </c>
       <c r="E113">
-        <v>0.4999685173837467</v>
+        <v>0.1193450572768154</v>
       </c>
       <c r="F113">
-        <v>0.499215104961316</v>
+        <v>0.8583764396915905</v>
       </c>
       <c r="G113">
-        <v>0.3322092786322394</v>
+        <v>0.05566712569026076</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -3129,19 +3129,19 @@
         <v>2015</v>
       </c>
       <c r="C114">
-        <v>0.2148049644404421</v>
+        <v>0.7465080913290234</v>
       </c>
       <c r="D114">
-        <v>0.1098928779063743</v>
+        <v>0.8740841043249498</v>
       </c>
       <c r="E114">
-        <v>0.481420694295541</v>
+        <v>0.07334841811688368</v>
       </c>
       <c r="F114">
-        <v>0.4954289584225158</v>
+        <v>0.8384615772454282</v>
       </c>
       <c r="G114">
-        <v>0.3877381890486456</v>
+        <v>0.2662166877234538</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -3152,19 +3152,19 @@
         <v>2015</v>
       </c>
       <c r="C115">
-        <v>0.2249904305836613</v>
+        <v>0.8910814672119608</v>
       </c>
       <c r="D115">
-        <v>0.102132115436108</v>
+        <v>0.6722850550885884</v>
       </c>
       <c r="E115">
-        <v>0.5038756277401182</v>
+        <v>0.1365445001619598</v>
       </c>
       <c r="F115">
-        <v>0.4819234058338915</v>
+        <v>0.7359285152480507</v>
       </c>
       <c r="G115">
-        <v>0.3826371749255492</v>
+        <v>0.2173518052425683</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -3175,19 +3175,19 @@
         <v>2015</v>
       </c>
       <c r="C116">
-        <v>0.1597647571680174</v>
+        <v>0.04140363908322559</v>
       </c>
       <c r="D116">
-        <v>0.0690883110574492</v>
+        <v>0.03726231398913385</v>
       </c>
       <c r="E116">
-        <v>0.5754640331833829</v>
+        <v>0.8724346359468684</v>
       </c>
       <c r="F116">
-        <v>0.4448049635528029</v>
+        <v>0.2895521347817166</v>
       </c>
       <c r="G116">
-        <v>0.356763045246973</v>
+        <v>0.08696315435065055</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -3198,19 +3198,19 @@
         <v>2015</v>
       </c>
       <c r="C117">
-        <v>0.2104118680001053</v>
+        <v>0.634913430166038</v>
       </c>
       <c r="D117">
-        <v>0.09053932185076005</v>
+        <v>0.2158594657030836</v>
       </c>
       <c r="E117">
-        <v>0.5825146745506565</v>
+        <v>0.9002670264635485</v>
       </c>
       <c r="F117">
-        <v>0.4622445999987964</v>
+        <v>0.5020718718966395</v>
       </c>
       <c r="G117">
-        <v>0.4450081012070794</v>
+        <v>0.8806081006046853</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -3221,19 +3221,19 @@
         <v>2015</v>
       </c>
       <c r="C118">
-        <v>0.2010801327952157</v>
+        <v>0.3508500563979376</v>
       </c>
       <c r="D118">
-        <v>0.09574057030683751</v>
+        <v>0.4010975113692861</v>
       </c>
       <c r="E118">
-        <v>0.5279290935936433</v>
+        <v>0.3438918461357556</v>
       </c>
       <c r="F118">
-        <v>0.4919289514162926</v>
+        <v>0.8168523650683082</v>
       </c>
       <c r="G118">
-        <v>0.3709651702120115</v>
+        <v>0.1379349636653613</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -3244,19 +3244,19 @@
         <v>2015</v>
       </c>
       <c r="C119">
-        <v>0.2241454271033674</v>
+        <v>0.8840952672920884</v>
       </c>
       <c r="D119">
-        <v>0.0915812487647145</v>
+        <v>0.2464894295784169</v>
       </c>
       <c r="E119">
-        <v>0.5311816824925383</v>
+        <v>0.386380756002795</v>
       </c>
       <c r="F119">
-        <v>0.4462245570757371</v>
+        <v>0.3044643522337198</v>
       </c>
       <c r="G119">
-        <v>0.4271775743179829</v>
+        <v>0.7653156166320236</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -3267,19 +3267,19 @@
         <v>2015</v>
       </c>
       <c r="C120">
-        <v>0.1801561788126231</v>
+        <v>0.06633082586775708</v>
       </c>
       <c r="D120">
-        <v>0.09830290453825428</v>
+        <v>0.5125845778905687</v>
       </c>
       <c r="E120">
-        <v>0.5925599109606098</v>
+        <v>0.9251041977775054</v>
       </c>
       <c r="F120">
-        <v>0.5030180939365586</v>
+        <v>0.8751557114597629</v>
       </c>
       <c r="G120">
-        <v>0.3860653423352003</v>
+        <v>0.2491902497008031</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -3290,19 +3290,19 @@
         <v>2015</v>
       </c>
       <c r="C121">
-        <v>0.2153750860945969</v>
+        <v>0.7587369707616989</v>
       </c>
       <c r="D121">
-        <v>0.1036415575065098</v>
+        <v>0.7260790742142936</v>
       </c>
       <c r="E121">
-        <v>0.555604753401118</v>
+        <v>0.7179494818372623</v>
       </c>
       <c r="F121">
-        <v>0.4139017295616953</v>
+        <v>0.1005631424088023</v>
       </c>
       <c r="G121">
-        <v>0.3864579432816155</v>
+        <v>0.2530987289383432</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -3313,19 +3313,19 @@
         <v>2015</v>
       </c>
       <c r="C122">
-        <v>0.2128953622643715</v>
+        <v>0.7016324239971958</v>
       </c>
       <c r="D122">
-        <v>0.1079725099127656</v>
+        <v>0.8407717687550835</v>
       </c>
       <c r="E122">
-        <v>0.5059617696901034</v>
+        <v>0.1472530014445174</v>
       </c>
       <c r="F122">
-        <v>0.4349654172947494</v>
+        <v>0.2024187865326899</v>
       </c>
       <c r="G122">
-        <v>0.4447842105005546</v>
+        <v>0.8796927908446932</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -3336,19 +3336,19 @@
         <v>2015</v>
       </c>
       <c r="C123">
-        <v>0.2283293839007801</v>
+        <v>0.9127906746933109</v>
       </c>
       <c r="D123">
-        <v>0.1130980710681412</v>
+        <v>0.9117796002400117</v>
       </c>
       <c r="E123">
-        <v>0.4954340735727395</v>
+        <v>0.1034008523359679</v>
       </c>
       <c r="F123">
-        <v>0.391566304368743</v>
+        <v>0.06353093016624792</v>
       </c>
       <c r="G123">
-        <v>0.3985104529441552</v>
+        <v>0.3971066921205967</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -3359,19 +3359,19 @@
         <v>2015</v>
       </c>
       <c r="C124">
-        <v>0.1997350023914813</v>
+        <v>0.3139756011706227</v>
       </c>
       <c r="D124">
-        <v>0.09426304501039366</v>
+        <v>0.3409522453538729</v>
       </c>
       <c r="E124">
-        <v>0.5818404153595821</v>
+        <v>0.8980427290218551</v>
       </c>
       <c r="F124">
-        <v>0.4159118865090922</v>
+        <v>0.1064997151622653</v>
       </c>
       <c r="G124">
-        <v>0.4351450233050824</v>
+        <v>0.8285743787099352</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -3382,19 +3382,19 @@
         <v>2015</v>
       </c>
       <c r="C125">
-        <v>0.2046509105573023</v>
+        <v>0.458197184942172</v>
       </c>
       <c r="D125">
-        <v>0.09181959502970949</v>
+        <v>0.2539908420744615</v>
       </c>
       <c r="E125">
-        <v>0.5468792492631263</v>
+        <v>0.608578845311704</v>
       </c>
       <c r="F125">
-        <v>0.4569918910821247</v>
+        <v>0.4331880145137182</v>
       </c>
       <c r="G125">
-        <v>0.3704184684378366</v>
+        <v>0.1351867866013942</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -3405,19 +3405,19 @@
         <v>2015</v>
       </c>
       <c r="C126">
-        <v>0.1767006915075476</v>
+        <v>0.05658903633752767</v>
       </c>
       <c r="D126">
-        <v>0.07742066060451669</v>
+        <v>0.05282094325898157</v>
       </c>
       <c r="E126">
-        <v>0.5329725016671819</v>
+        <v>0.4108386208525981</v>
       </c>
       <c r="F126">
-        <v>0.4809988521506465</v>
+        <v>0.7269537011807263</v>
       </c>
       <c r="G126">
-        <v>0.4264990523038789</v>
+        <v>0.7589284302644324</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -3428,19 +3428,19 @@
         <v>2015</v>
       </c>
       <c r="C127">
-        <v>0.1896756938356223</v>
+        <v>0.1288389001265294</v>
       </c>
       <c r="D127">
-        <v>0.08988134581285695</v>
+        <v>0.1983269670406714</v>
       </c>
       <c r="E127">
-        <v>0.5262755873840543</v>
+        <v>0.3234215737037308</v>
       </c>
       <c r="F127">
-        <v>0.5030706803075835</v>
+        <v>0.8753670671708711</v>
       </c>
       <c r="G127">
-        <v>0.3919754173485359</v>
+        <v>0.313591359023887</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -3451,19 +3451,19 @@
         <v>2015</v>
       </c>
       <c r="C128">
-        <v>0.1684448695161957</v>
+        <v>0.04519216232554146</v>
       </c>
       <c r="D128">
-        <v>0.08509594375863455</v>
+        <v>0.108625106314937</v>
       </c>
       <c r="E128">
-        <v>0.5644855676832149</v>
+        <v>0.8033143205777893</v>
       </c>
       <c r="F128">
-        <v>0.5129723048148929</v>
+        <v>0.9067943672321463</v>
       </c>
       <c r="G128">
-        <v>0.4034945691672834</v>
+        <v>0.4666157898313497</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -3474,19 +3474,19 @@
         <v>2015</v>
       </c>
       <c r="C129">
-        <v>0.2477016057040317</v>
+        <v>0.9512244746452678</v>
       </c>
       <c r="D129">
-        <v>0.1254317828048505</v>
+        <v>0.9583193798280121</v>
       </c>
       <c r="E129">
-        <v>0.4990783560521052</v>
+        <v>0.115899100501797</v>
       </c>
       <c r="F129">
-        <v>0.4259828725679787</v>
+        <v>0.1469041635918537</v>
       </c>
       <c r="G129">
-        <v>0.4138535548259076</v>
+        <v>0.6121677162274582</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -3497,19 +3497,19 @@
         <v>2015</v>
       </c>
       <c r="C130">
-        <v>0.2227454002806429</v>
+        <v>0.8709234523211022</v>
       </c>
       <c r="D130">
-        <v>0.1098538557991757</v>
+        <v>0.8734978266667084</v>
       </c>
       <c r="E130">
-        <v>0.5409986437921136</v>
+        <v>0.5254791395666366</v>
       </c>
       <c r="F130">
-        <v>0.4331130464570996</v>
+        <v>0.1891982797181977</v>
       </c>
       <c r="G130">
-        <v>0.4527596689116334</v>
+        <v>0.9063811833345679</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -3520,19 +3520,19 @@
         <v>2015</v>
       </c>
       <c r="C131">
-        <v>0.2068303496859452</v>
+        <v>0.5266978921976809</v>
       </c>
       <c r="D131">
-        <v>0.09166112955999733</v>
+        <v>0.248983089646738</v>
       </c>
       <c r="E131">
-        <v>0.6301809008224868</v>
+        <v>0.9524277544376899</v>
       </c>
       <c r="F131">
-        <v>0.3953099057607097</v>
+        <v>0.06710548747710535</v>
       </c>
       <c r="G131">
-        <v>0.4703843543500496</v>
+        <v>0.9361886965548658</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -3543,19 +3543,19 @@
         <v>2015</v>
       </c>
       <c r="C132">
-        <v>0.1931587091702363</v>
+        <v>0.174931501736916</v>
       </c>
       <c r="D132">
-        <v>0.08835518533715324</v>
+        <v>0.1628786745039122</v>
       </c>
       <c r="E132">
-        <v>0.5788748427182848</v>
+        <v>0.8872203667368664</v>
       </c>
       <c r="F132">
-        <v>0.5026930645516655</v>
+        <v>0.873837389222182</v>
       </c>
       <c r="G132">
-        <v>0.4742511765194108</v>
+        <v>0.9395562497520663</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -3566,19 +3566,19 @@
         <v>2015</v>
       </c>
       <c r="C133">
-        <v>0.192952693808239</v>
+        <v>0.1717188409410708</v>
       </c>
       <c r="D133">
-        <v>0.109890395983615</v>
+        <v>0.8740469194601621</v>
       </c>
       <c r="E133">
-        <v>0.5335119359033821</v>
+        <v>0.4183278548579069</v>
       </c>
       <c r="F133">
-        <v>0.4559813232878088</v>
+        <v>0.4201966704794605</v>
       </c>
       <c r="G133">
-        <v>0.4138346682899386</v>
+        <v>0.6119147188506073</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -3589,19 +3589,19 @@
         <v>2015</v>
       </c>
       <c r="C134">
-        <v>0.1921544220013019</v>
+        <v>0.1598784541492267</v>
       </c>
       <c r="D134">
-        <v>0.09614997373636926</v>
+        <v>0.4184918904843353</v>
       </c>
       <c r="E134">
-        <v>0.5900492743219428</v>
+        <v>0.9201589482947208</v>
       </c>
       <c r="F134">
-        <v>0.4910023010210693</v>
+        <v>0.8105785158336645</v>
       </c>
       <c r="G134">
-        <v>0.4523783327887419</v>
+        <v>0.9053517136415545</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -3612,19 +3612,19 @@
         <v>2015</v>
       </c>
       <c r="C135">
-        <v>0.1862610385239473</v>
+        <v>0.09800228681337897</v>
       </c>
       <c r="D135">
-        <v>0.06129133405700727</v>
+        <v>0.03399082075755303</v>
       </c>
       <c r="E135">
-        <v>0.50662706228091</v>
+        <v>0.1509116099744394</v>
       </c>
       <c r="F135">
-        <v>0.4985355170883681</v>
+        <v>0.8550497881122312</v>
       </c>
       <c r="G135">
-        <v>0.401139591997779</v>
+        <v>0.433366576291393</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -3635,19 +3635,19 @@
         <v>2015</v>
       </c>
       <c r="C136">
-        <v>0.2205209264254758</v>
+        <v>0.8452982625725818</v>
       </c>
       <c r="D136">
-        <v>0.09277710070894397</v>
+        <v>0.2859460690068513</v>
       </c>
       <c r="E136">
-        <v>0.5506153964487642</v>
+        <v>0.6580702416219506</v>
       </c>
       <c r="F136">
-        <v>0.440700926672344</v>
+        <v>0.2497126764671491</v>
       </c>
       <c r="G136">
-        <v>0.4393464447390632</v>
+        <v>0.8538775443458377</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -3658,19 +3658,19 @@
         <v>2015</v>
       </c>
       <c r="C137">
-        <v>0.2025514628269852</v>
+        <v>0.3937434643106341</v>
       </c>
       <c r="D137">
-        <v>0.09083578664427788</v>
+        <v>0.2242157723519677</v>
       </c>
       <c r="E137">
-        <v>0.4847367528554754</v>
+        <v>0.0784591680507454</v>
       </c>
       <c r="F137">
-        <v>0.5126472729069543</v>
+        <v>0.905992514529796</v>
       </c>
       <c r="G137">
-        <v>0.362535831406558</v>
+        <v>0.1031409130274087</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -3681,19 +3681,19 @@
         <v>2015</v>
       </c>
       <c r="C138">
-        <v>0.2161862223311087</v>
+        <v>0.7751979271479132</v>
       </c>
       <c r="D138">
-        <v>0.09531930328994309</v>
+        <v>0.3834909355484445</v>
       </c>
       <c r="E138">
-        <v>0.5033526840324057</v>
+        <v>0.1340342453299906</v>
       </c>
       <c r="F138">
-        <v>0.4301441889576418</v>
+        <v>0.1699926722396988</v>
       </c>
       <c r="G138">
-        <v>0.4098931762903849</v>
+        <v>0.5576914901806874</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -3704,19 +3704,19 @@
         <v>2015</v>
       </c>
       <c r="C139">
-        <v>0.1769323037335385</v>
+        <v>0.05711740078861985</v>
       </c>
       <c r="D139">
-        <v>0.09278622577258239</v>
+        <v>0.2862643329944193</v>
       </c>
       <c r="E139">
-        <v>0.5907266842254183</v>
+        <v>0.9215644397711829</v>
       </c>
       <c r="F139">
-        <v>0.5173494703498893</v>
+        <v>0.9163777146715628</v>
       </c>
       <c r="G139">
-        <v>0.3406222089970731</v>
+        <v>0.06187214241774833</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -3727,19 +3727,19 @@
         <v>2015</v>
       </c>
       <c r="C140">
-        <v>0.193864389664563</v>
+        <v>0.1864387679558094</v>
       </c>
       <c r="D140">
-        <v>0.1044876927064861</v>
+        <v>0.7531685859399739</v>
       </c>
       <c r="E140">
-        <v>0.5233390648171878</v>
+        <v>0.28920289372903</v>
       </c>
       <c r="F140">
-        <v>0.4951449697062263</v>
+        <v>0.8368271991260718</v>
       </c>
       <c r="G140">
-        <v>0.4161500371607145</v>
+        <v>0.6423206788286113</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -3750,19 +3750,19 @@
         <v>2015</v>
       </c>
       <c r="C141">
-        <v>0.2237397534835946</v>
+        <v>0.8804917700128851</v>
       </c>
       <c r="D141">
-        <v>0.1250155085499913</v>
+        <v>0.9578546065623711</v>
       </c>
       <c r="E141">
-        <v>0.5160782758143294</v>
+        <v>0.2174189629953584</v>
       </c>
       <c r="F141">
-        <v>0.4183793215223546</v>
+        <v>0.1146531506578899</v>
       </c>
       <c r="G141">
-        <v>0.4057393043025529</v>
+        <v>0.4986476580746977</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -3773,19 +3773,19 @@
         <v>2015</v>
       </c>
       <c r="C142">
-        <v>0.216367714819959</v>
+        <v>0.778730839680654</v>
       </c>
       <c r="D142">
-        <v>0.09513922282647165</v>
+        <v>0.3760667502111718</v>
       </c>
       <c r="E142">
-        <v>0.5516986710061808</v>
+        <v>0.67172985840907</v>
       </c>
       <c r="F142">
-        <v>0.4281753621220725</v>
+        <v>0.1585361515790511</v>
       </c>
       <c r="G142">
-        <v>0.4575538599890933</v>
+        <v>0.9176194106751818</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -3796,19 +3796,19 @@
         <v>2015</v>
       </c>
       <c r="C143">
-        <v>0.2019762699795854</v>
+        <v>0.3766953844816252</v>
       </c>
       <c r="D143">
-        <v>0.08453819603228918</v>
+        <v>0.1017765864856295</v>
       </c>
       <c r="E143">
-        <v>0.5119626640628711</v>
+        <v>0.184931522929965</v>
       </c>
       <c r="F143">
-        <v>0.4621222038498392</v>
+        <v>0.5004550548133644</v>
       </c>
       <c r="G143">
-        <v>0.4199904105056586</v>
+        <v>0.6895969157659254</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -3819,19 +3819,19 @@
         <v>2015</v>
       </c>
       <c r="C144">
-        <v>0.1973650112737163</v>
+        <v>0.2556155581678857</v>
       </c>
       <c r="D144">
-        <v>0.09393844602697049</v>
+        <v>0.3284152346328887</v>
       </c>
       <c r="E144">
-        <v>0.549450060149451</v>
+        <v>0.6430080344263371</v>
       </c>
       <c r="F144">
-        <v>0.428384658654804</v>
+        <v>0.1597075186066944</v>
       </c>
       <c r="G144">
-        <v>0.3731985221960017</v>
+        <v>0.1499767584630745</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -3842,19 +3842,19 @@
         <v>2015</v>
       </c>
       <c r="C145">
-        <v>0.2235464612347056</v>
+        <v>0.8787151527274836</v>
       </c>
       <c r="D145">
-        <v>0.09698937161898466</v>
+        <v>0.4548263733122055</v>
       </c>
       <c r="E145">
-        <v>0.5226910267373568</v>
+        <v>0.282040805653852</v>
       </c>
       <c r="F145">
-        <v>0.4357122180163829</v>
+        <v>0.2080270116200427</v>
       </c>
       <c r="G145">
-        <v>0.412125089445842</v>
+        <v>0.58871784340467</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -3865,19 +3865,19 @@
         <v>2015</v>
       </c>
       <c r="C146">
-        <v>0.1836115725892709</v>
+        <v>0.08133350812830514</v>
       </c>
       <c r="D146">
-        <v>0.1147691227031661</v>
+        <v>0.9248864257318617</v>
       </c>
       <c r="E146">
-        <v>0.5832443555473437</v>
+        <v>0.902582307998063</v>
       </c>
       <c r="F146">
-        <v>0.4863810628407251</v>
+        <v>0.775628331848957</v>
       </c>
       <c r="G146">
-        <v>0.4004629450083578</v>
+        <v>0.4239304193715944</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -3888,19 +3888,19 @@
         <v>2015</v>
       </c>
       <c r="C147">
-        <v>0.2169258127007373</v>
+        <v>0.7892533359602726</v>
       </c>
       <c r="D147">
-        <v>0.09904374312908068</v>
+        <v>0.5450691760908275</v>
       </c>
       <c r="E147">
-        <v>0.5211222562283196</v>
+        <v>0.2653075258918953</v>
       </c>
       <c r="F147">
-        <v>0.4204209766347819</v>
+        <v>0.122192393997638</v>
       </c>
       <c r="G147">
-        <v>0.430251584062123</v>
+        <v>0.7922479424237265</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -3911,19 +3911,19 @@
         <v>2015</v>
       </c>
       <c r="C148">
-        <v>0.212141604929617</v>
+        <v>0.6823197120046726</v>
       </c>
       <c r="D148">
-        <v>0.1078733636531096</v>
+        <v>0.8387873378639794</v>
       </c>
       <c r="E148">
-        <v>0.4686050818793299</v>
+        <v>0.06080198437384783</v>
       </c>
       <c r="F148">
-        <v>0.500357414600797</v>
+        <v>0.863736793576664</v>
       </c>
       <c r="G148">
-        <v>0.4158525679592935</v>
+        <v>0.6384871359124961</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -3934,19 +3934,19 @@
         <v>2015</v>
       </c>
       <c r="C149">
-        <v>0.2093997307457287</v>
+        <v>0.6054438079250579</v>
       </c>
       <c r="D149">
-        <v>0.09912224617100064</v>
+        <v>0.5484895986700327</v>
       </c>
       <c r="E149">
-        <v>0.568963158721382</v>
+        <v>0.8359389753360835</v>
       </c>
       <c r="F149">
-        <v>0.480648413771839</v>
+        <v>0.7234863675602681</v>
       </c>
       <c r="G149">
-        <v>0.390167519813332</v>
+        <v>0.2926522387389652</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -3957,19 +3957,19 @@
         <v>2015</v>
       </c>
       <c r="C150">
-        <v>0.1964841531401726</v>
+        <v>0.236271804265315</v>
       </c>
       <c r="D150">
-        <v>0.09322021527446796</v>
+        <v>0.3016902753420783</v>
       </c>
       <c r="E150">
-        <v>0.6093740307433045</v>
+        <v>0.9446524943560387</v>
       </c>
       <c r="F150">
-        <v>0.4227457931783389</v>
+        <v>0.1317371290901413</v>
       </c>
       <c r="G150">
-        <v>0.4453099189046498</v>
+        <v>0.8818250295883003</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -3980,19 +3980,19 @@
         <v>2015</v>
       </c>
       <c r="C151">
-        <v>0.2118792718627631</v>
+        <v>0.6753977230061889</v>
       </c>
       <c r="D151">
-        <v>0.09981668490254136</v>
+        <v>0.5784620376562836</v>
       </c>
       <c r="E151">
-        <v>0.5236135925998985</v>
+        <v>0.2922803655851521</v>
       </c>
       <c r="F151">
-        <v>0.4906172694592508</v>
+        <v>0.8079012123786266</v>
       </c>
       <c r="G151">
-        <v>0.3526683417878501</v>
+        <v>0.07826881599154507</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -4003,19 +4003,19 @@
         <v>2015</v>
       </c>
       <c r="C152">
-        <v>0.2024741807690513</v>
+        <v>0.3914340694748123</v>
       </c>
       <c r="D152">
-        <v>0.1054762589358323</v>
+        <v>0.7819000969572389</v>
       </c>
       <c r="E152">
-        <v>0.5428559033905911</v>
+        <v>0.5521627951837212</v>
       </c>
       <c r="F152">
-        <v>0.4995016883671233</v>
+        <v>0.859748207693034</v>
       </c>
       <c r="G152">
-        <v>0.3636563783001262</v>
+        <v>0.1069194773476688</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -4026,19 +4026,19 @@
         <v>2015</v>
       </c>
       <c r="C153">
-        <v>0.2290250951927441</v>
+        <v>0.9163194029341977</v>
       </c>
       <c r="D153">
-        <v>0.1017201835517844</v>
+        <v>0.6564836349898666</v>
       </c>
       <c r="E153">
-        <v>0.524393681143666</v>
+        <v>0.3011644218739918</v>
       </c>
       <c r="F153">
-        <v>0.3787917869731068</v>
+        <v>0.05567544855844029</v>
       </c>
       <c r="G153">
-        <v>0.475741158544189</v>
+        <v>0.9406598873988828</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -4049,19 +4049,19 @@
         <v>2015</v>
       </c>
       <c r="C154">
-        <v>0.1917315784872413</v>
+        <v>0.153987530052872</v>
       </c>
       <c r="D154">
-        <v>0.07974119306850459</v>
+        <v>0.06290733665897678</v>
       </c>
       <c r="E154">
-        <v>0.5732819505936614</v>
+        <v>0.8614895223725308</v>
       </c>
       <c r="F154">
-        <v>0.4329695161002394</v>
+        <v>0.1882143367627878</v>
       </c>
       <c r="G154">
-        <v>0.4202421587434275</v>
+        <v>0.6925413802904141</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -4072,19 +4072,19 @@
         <v>2018</v>
       </c>
       <c r="C155">
-        <v>0.2363995634196888</v>
+        <v>0.9213661784484685</v>
       </c>
       <c r="D155">
-        <v>0.1298821994753725</v>
+        <v>0.9550109019292138</v>
       </c>
       <c r="E155">
-        <v>0.4608762453846766</v>
+        <v>0.07255217365980221</v>
       </c>
       <c r="F155">
-        <v>0.4574317936694959</v>
+        <v>0.4664932206699976</v>
       </c>
       <c r="G155">
-        <v>0.4463627255776136</v>
+        <v>0.6956450136348817</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -4095,19 +4095,19 @@
         <v>2018</v>
       </c>
       <c r="C156">
-        <v>0.2512159568353572</v>
+        <v>0.9601303601605894</v>
       </c>
       <c r="D156">
-        <v>0.1212678806148139</v>
+        <v>0.9294679180570939</v>
       </c>
       <c r="E156">
-        <v>0.5263694191403177</v>
+        <v>0.7692933048412609</v>
       </c>
       <c r="F156">
-        <v>0.4662046144223658</v>
+        <v>0.6559741917062828</v>
       </c>
       <c r="G156">
-        <v>0.3678811395463695</v>
+        <v>0.04558042408096716</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -4118,19 +4118,19 @@
         <v>2018</v>
       </c>
       <c r="C157">
-        <v>0.1965372538401743</v>
+        <v>0.1558631872184471</v>
       </c>
       <c r="D157">
-        <v>0.08202382560705529</v>
+        <v>0.1143563519207206</v>
       </c>
       <c r="E157">
-        <v>0.5095616326246609</v>
+        <v>0.5108501997445962</v>
       </c>
       <c r="F157">
-        <v>0.4517995899674293</v>
+        <v>0.3470107769520649</v>
       </c>
       <c r="G157">
-        <v>0.4596158768563898</v>
+        <v>0.8348786200833622</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -4141,19 +4141,19 @@
         <v>2018</v>
       </c>
       <c r="C158">
-        <v>0.2190922555180406</v>
+        <v>0.6826100918558172</v>
       </c>
       <c r="D158">
-        <v>0.09944085756556907</v>
+        <v>0.5112046047646404</v>
       </c>
       <c r="E158">
-        <v>0.4784007046353585</v>
+        <v>0.1258981695322751</v>
       </c>
       <c r="F158">
-        <v>0.4629076194897538</v>
+        <v>0.5876544313640116</v>
       </c>
       <c r="G158">
-        <v>0.4466845222583886</v>
+        <v>0.6999822639496347</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -4164,19 +4164,19 @@
         <v>2018</v>
       </c>
       <c r="C159">
-        <v>0.19000548286689</v>
+        <v>0.09758852293156978</v>
       </c>
       <c r="D159">
-        <v>0.07829916208565983</v>
+        <v>0.08656347185684365</v>
       </c>
       <c r="E159">
-        <v>0.4933788267820092</v>
+        <v>0.2534781155641254</v>
       </c>
       <c r="F159">
-        <v>0.5007453111418931</v>
+        <v>0.9428788075499721</v>
       </c>
       <c r="G159">
-        <v>0.4060996099716389</v>
+        <v>0.1465323550421377</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -4187,19 +4187,19 @@
         <v>2018</v>
       </c>
       <c r="C160">
-        <v>0.2113831607182657</v>
+        <v>0.4711687421798487</v>
       </c>
       <c r="D160">
-        <v>0.1084943629373591</v>
+        <v>0.7762965879842512</v>
       </c>
       <c r="E160">
-        <v>0.5367732917492171</v>
+        <v>0.8600345611645933</v>
       </c>
       <c r="F160">
-        <v>0.4321763308293939</v>
+        <v>0.1069736601547743</v>
       </c>
       <c r="G160">
-        <v>0.4192223122558204</v>
+        <v>0.2752099309649221</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -4210,19 +4210,19 @@
         <v>2018</v>
       </c>
       <c r="C161">
-        <v>0.1942652285909758</v>
+        <v>0.1311754238581161</v>
       </c>
       <c r="D161">
-        <v>0.0918616917465314</v>
+        <v>0.2783327571823867</v>
       </c>
       <c r="E161">
-        <v>0.501164774285903</v>
+        <v>0.3653459965646462</v>
       </c>
       <c r="F161">
-        <v>0.4738293412376292</v>
+        <v>0.7844181121754534</v>
       </c>
       <c r="G161">
-        <v>0.3811601578653735</v>
+        <v>0.05806169071864549</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -4233,19 +4233,19 @@
         <v>2018</v>
       </c>
       <c r="C162">
-        <v>0.218228408406403</v>
+        <v>0.6610184896771444</v>
       </c>
       <c r="D162">
-        <v>0.1038410499406023</v>
+        <v>0.6539509034366265</v>
       </c>
       <c r="E162">
-        <v>0.5068601156032371</v>
+        <v>0.4626958556993208</v>
       </c>
       <c r="F162">
-        <v>0.4627048916719497</v>
+        <v>0.5832807781928339</v>
       </c>
       <c r="G162">
-        <v>0.444208390826569</v>
+        <v>0.6654778811977078</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -4256,19 +4256,19 @@
         <v>2018</v>
       </c>
       <c r="C163">
-        <v>0.2312474812765324</v>
+        <v>0.8844103515792654</v>
       </c>
       <c r="D163">
-        <v>0.1270811289187477</v>
+        <v>0.9496470317226716</v>
       </c>
       <c r="E163">
-        <v>0.5285715289148368</v>
+        <v>0.7930805394808713</v>
       </c>
       <c r="F163">
-        <v>0.4915182800143567</v>
+        <v>0.9210025978100564</v>
       </c>
       <c r="G163">
-        <v>0.4034926530877236</v>
+        <v>0.1297678488504698</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -4279,19 +4279,19 @@
         <v>2018</v>
       </c>
       <c r="C164">
-        <v>0.1938373198555404</v>
+        <v>0.127106947652054</v>
       </c>
       <c r="D164">
-        <v>0.07670602699877034</v>
+        <v>0.07812658262749501</v>
       </c>
       <c r="E164">
-        <v>0.5302608002351119</v>
+        <v>0.809565088243749</v>
       </c>
       <c r="F164">
-        <v>0.4929872517966162</v>
+        <v>0.9257737311219384</v>
       </c>
       <c r="G164">
-        <v>0.3583407332595517</v>
+        <v>0.04158725205771355</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -4302,19 +4302,19 @@
         <v>2018</v>
       </c>
       <c r="C165">
-        <v>0.2129257351018593</v>
+        <v>0.5152475901856413</v>
       </c>
       <c r="D165">
-        <v>0.08819203170236159</v>
+        <v>0.1979099243483176</v>
       </c>
       <c r="E165">
-        <v>0.480543341710558</v>
+        <v>0.1379651870307954</v>
       </c>
       <c r="F165">
-        <v>0.4649599765436121</v>
+        <v>0.6308838337369952</v>
       </c>
       <c r="G165">
-        <v>0.4559939021144498</v>
+        <v>0.804791044822634</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -4325,19 +4325,19 @@
         <v>2018</v>
       </c>
       <c r="C166">
-        <v>0.2397218784266969</v>
+        <v>0.9362694737662357</v>
       </c>
       <c r="D166">
-        <v>0.1127118554930647</v>
+        <v>0.8525661491232129</v>
       </c>
       <c r="E166">
-        <v>0.4555067405573756</v>
+        <v>0.06581566729029902</v>
       </c>
       <c r="F166">
-        <v>0.4750683242440156</v>
+        <v>0.8007529473000476</v>
       </c>
       <c r="G166">
-        <v>0.4302363300599898</v>
+        <v>0.440152935704873</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -4348,19 +4348,19 @@
         <v>2018</v>
       </c>
       <c r="C167">
-        <v>0.1793426255400813</v>
+        <v>0.05789107511548159</v>
       </c>
       <c r="D167">
-        <v>0.07188937531123808</v>
+        <v>0.06103415971913641</v>
       </c>
       <c r="E167">
-        <v>0.5369599533895819</v>
+        <v>0.8612049081296894</v>
       </c>
       <c r="F167">
-        <v>0.501979800680133</v>
+        <v>0.9446665905307545</v>
       </c>
       <c r="G167">
-        <v>0.3425031205347423</v>
+        <v>0.03892826256858795</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -4371,19 +4371,19 @@
         <v>2018</v>
       </c>
       <c r="C168">
-        <v>0.2227203731178575</v>
+        <v>0.763200343381249</v>
       </c>
       <c r="D168">
-        <v>0.09037011349445923</v>
+        <v>0.2425906087071938</v>
       </c>
       <c r="E168">
-        <v>0.5175651625594772</v>
+        <v>0.6481464989475799</v>
       </c>
       <c r="F168">
-        <v>0.4119300899443256</v>
+        <v>0.05278463072355214</v>
       </c>
       <c r="G168">
-        <v>0.4720711459882177</v>
+        <v>0.9019611565367509</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -4394,19 +4394,19 @@
         <v>2018</v>
       </c>
       <c r="C169">
-        <v>0.1885800636740715</v>
+        <v>0.08929315796273229</v>
       </c>
       <c r="D169">
-        <v>0.0882696016210274</v>
+        <v>0.1993503998660412</v>
       </c>
       <c r="E169">
-        <v>0.4981598149661599</v>
+        <v>0.3186118856196286</v>
       </c>
       <c r="F169">
-        <v>0.4741111134691865</v>
+        <v>0.788245155856091</v>
       </c>
       <c r="G169">
-        <v>0.3956287676513678</v>
+        <v>0.09251556550005868</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -4417,19 +4417,19 @@
         <v>2018</v>
       </c>
       <c r="C170">
-        <v>0.2200052588983606</v>
+        <v>0.7044880130649827</v>
       </c>
       <c r="D170">
-        <v>0.1082478587911925</v>
+        <v>0.7708161779656482</v>
       </c>
       <c r="E170">
-        <v>0.4887935561784241</v>
+        <v>0.2026574810331899</v>
       </c>
       <c r="F170">
-        <v>0.4613100516321673</v>
+        <v>0.5528083102469485</v>
       </c>
       <c r="G170">
-        <v>0.4612072980062551</v>
+        <v>0.8463751488461706</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -4440,19 +4440,19 @@
         <v>2018</v>
       </c>
       <c r="C171">
-        <v>0.2128564879780749</v>
+        <v>0.5132657039327518</v>
       </c>
       <c r="D171">
-        <v>0.09116599357663338</v>
+        <v>0.261142667415912</v>
       </c>
       <c r="E171">
-        <v>0.5339127969595646</v>
+        <v>0.8402721507131508</v>
       </c>
       <c r="F171">
-        <v>0.4351348897649585</v>
+        <v>0.1258906692213728</v>
       </c>
       <c r="G171">
-        <v>0.4829031056805793</v>
+        <v>0.9301913636466144</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -4463,19 +4463,19 @@
         <v>2018</v>
       </c>
       <c r="C172">
-        <v>0.2261400213405703</v>
+        <v>0.8228198326772164</v>
       </c>
       <c r="D172">
-        <v>0.1195121903729756</v>
+        <v>0.9196492549020253</v>
       </c>
       <c r="E172">
-        <v>0.5412581102961437</v>
+        <v>0.8845678104886965</v>
       </c>
       <c r="F172">
-        <v>0.4865099925375445</v>
+        <v>0.8993491052885454</v>
       </c>
       <c r="G172">
-        <v>0.4205672935446678</v>
+        <v>0.292911104984012</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -4486,19 +4486,19 @@
         <v>2018</v>
       </c>
       <c r="C173">
-        <v>0.2191452460814814</v>
+        <v>0.6839071205274044</v>
       </c>
       <c r="D173">
-        <v>0.1209144898139065</v>
+        <v>0.9276683294836173</v>
       </c>
       <c r="E173">
-        <v>0.4756441395879661</v>
+        <v>0.1126873348806163</v>
       </c>
       <c r="F173">
-        <v>0.4622191489562139</v>
+        <v>0.5727394100182432</v>
       </c>
       <c r="G173">
-        <v>0.4245645088772139</v>
+        <v>0.3500399664050323</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -4509,19 +4509,19 @@
         <v>2018</v>
       </c>
       <c r="C174">
-        <v>0.2482809448887114</v>
+        <v>0.9566242512404812</v>
       </c>
       <c r="D174">
-        <v>0.1403302736786578</v>
+        <v>0.9636699870220936</v>
       </c>
       <c r="E174">
-        <v>0.4659342395299385</v>
+        <v>0.08188220392184381</v>
       </c>
       <c r="F174">
-        <v>0.4189439968081565</v>
+        <v>0.06214071094722239</v>
       </c>
       <c r="G174">
-        <v>0.4624749011390844</v>
+        <v>0.8548327546887255</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -4532,19 +4532,19 @@
         <v>2018</v>
       </c>
       <c r="C175">
-        <v>0.209669027974565</v>
+        <v>0.422998073224568</v>
       </c>
       <c r="D175">
-        <v>0.09708861367589337</v>
+        <v>0.4326996254267016</v>
       </c>
       <c r="E175">
-        <v>0.5483092475692349</v>
+        <v>0.9108151938934537</v>
       </c>
       <c r="F175">
-        <v>0.4559765757365339</v>
+        <v>0.4344196015140175</v>
       </c>
       <c r="G175">
-        <v>0.4618077092877064</v>
+        <v>0.850456377451295</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -4555,19 +4555,19 @@
         <v>2018</v>
       </c>
       <c r="C176">
-        <v>0.2056671176102293</v>
+        <v>0.3191383021561816</v>
       </c>
       <c r="D176">
-        <v>0.1002528162037037</v>
+        <v>0.5384815028797769</v>
       </c>
       <c r="E176">
-        <v>0.4937278121197091</v>
+        <v>0.2578175574206956</v>
       </c>
       <c r="F176">
-        <v>0.4881360849735439</v>
+        <v>0.9074153430758265</v>
       </c>
       <c r="G176">
-        <v>0.4337862377216666</v>
+        <v>0.4993758991861976</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -4578,19 +4578,19 @@
         <v>2018</v>
       </c>
       <c r="C177">
-        <v>0.1882634376069109</v>
+        <v>0.08761555730822879</v>
       </c>
       <c r="D177">
-        <v>0.1003211481054361</v>
+        <v>0.5407696304470609</v>
       </c>
       <c r="E177">
-        <v>0.5180133233057643</v>
+        <v>0.6552421518253232</v>
       </c>
       <c r="F177">
-        <v>0.5173440838073243</v>
+        <v>0.9558601581293616</v>
       </c>
       <c r="G177">
-        <v>0.3927478541992184</v>
+        <v>0.08285496626447658</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -4601,19 +4601,19 @@
         <v>2018</v>
       </c>
       <c r="C178">
-        <v>0.1868912629248</v>
+        <v>0.08097064676004001</v>
       </c>
       <c r="D178">
-        <v>0.09231458733313022</v>
+        <v>0.2900030276530554</v>
       </c>
       <c r="E178">
-        <v>0.4960769894929862</v>
+        <v>0.2887526277517676</v>
       </c>
       <c r="F178">
-        <v>0.4633389497251499</v>
+        <v>0.5969045333492085</v>
       </c>
       <c r="G178">
-        <v>0.4898655712466057</v>
+        <v>0.9402285964845527</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -4624,19 +4624,19 @@
         <v>2018</v>
       </c>
       <c r="C179">
-        <v>0.1917745319166893</v>
+        <v>0.1097785933550894</v>
       </c>
       <c r="D179">
-        <v>0.08981758827979</v>
+        <v>0.2304151495152344</v>
       </c>
       <c r="E179">
-        <v>0.5390558453339729</v>
+        <v>0.873422170238551</v>
       </c>
       <c r="F179">
-        <v>0.4936961817787018</v>
+        <v>0.9278664528850558</v>
       </c>
       <c r="G179">
-        <v>0.4263222945221982</v>
+        <v>0.3770369914016308</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -4647,19 +4647,19 @@
         <v>2018</v>
       </c>
       <c r="C180">
-        <v>0.2869610418930207</v>
+        <v>0.9680876448848726</v>
       </c>
       <c r="D180">
-        <v>0.1445457983668119</v>
+        <v>0.9647597438371435</v>
       </c>
       <c r="E180">
-        <v>0.4582544446917265</v>
+        <v>0.068923888990556</v>
       </c>
       <c r="F180">
-        <v>0.4517002757904319</v>
+        <v>0.345050893081061</v>
       </c>
       <c r="G180">
-        <v>0.4777063156205221</v>
+        <v>0.9190683302744378</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -4670,19 +4670,19 @@
         <v>2018</v>
       </c>
       <c r="C181">
-        <v>0.2214729376972944</v>
+        <v>0.7374508076814967</v>
       </c>
       <c r="D181">
-        <v>0.1029868199919182</v>
+        <v>0.6276528775782177</v>
       </c>
       <c r="E181">
-        <v>0.4915944125177357</v>
+        <v>0.2323368646740703</v>
       </c>
       <c r="F181">
-        <v>0.4533737540932389</v>
+        <v>0.3788971412818053</v>
       </c>
       <c r="G181">
-        <v>0.4492250133214111</v>
+        <v>0.7325933539984646</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -4693,19 +4693,19 @@
         <v>2018</v>
       </c>
       <c r="C182">
-        <v>0.2058070976271955</v>
+        <v>0.3224898809584031</v>
       </c>
       <c r="D182">
-        <v>0.08974936766031796</v>
+        <v>0.2289518294712864</v>
       </c>
       <c r="E182">
-        <v>0.5500762328432814</v>
+        <v>0.9155964395005645</v>
       </c>
       <c r="F182">
-        <v>0.4390590600198808</v>
+        <v>0.1588639360616384</v>
       </c>
       <c r="G182">
-        <v>0.4830366790647322</v>
+        <v>0.9304304939373973</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -4716,19 +4716,19 @@
         <v>2018</v>
       </c>
       <c r="C183">
-        <v>0.1977046563888318</v>
+        <v>0.1707549385744044</v>
       </c>
       <c r="D183">
-        <v>0.08226137633909179</v>
+        <v>0.116600120507705</v>
       </c>
       <c r="E183">
-        <v>0.5620724646269369</v>
+        <v>0.9358884237539551</v>
       </c>
       <c r="F183">
-        <v>0.4705850351552853</v>
+        <v>0.7355337302226931</v>
       </c>
       <c r="G183">
-        <v>0.4534136813805559</v>
+        <v>0.7797976989295143</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -4739,19 +4739,19 @@
         <v>2018</v>
       </c>
       <c r="C184">
-        <v>0.2178202870878037</v>
+        <v>0.6505386065196194</v>
       </c>
       <c r="D184">
-        <v>0.1043293855772699</v>
+        <v>0.6685280786964787</v>
       </c>
       <c r="E184">
-        <v>0.4913648635879883</v>
+        <v>0.2297442864881993</v>
       </c>
       <c r="F184">
-        <v>0.4544945323302954</v>
+        <v>0.4024390803292047</v>
       </c>
       <c r="G184">
-        <v>0.4309523582805143</v>
+        <v>0.4520132064366452</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -4762,19 +4762,19 @@
         <v>2018</v>
       </c>
       <c r="C185">
-        <v>0.2139240384458565</v>
+        <v>0.5437536377050308</v>
       </c>
       <c r="D185">
-        <v>0.09227946506149715</v>
+        <v>0.2890846610364471</v>
       </c>
       <c r="E185">
-        <v>0.5553139474161002</v>
+        <v>0.9266661938974255</v>
       </c>
       <c r="F185">
-        <v>0.4642599147059987</v>
+        <v>0.6163738049649432</v>
       </c>
       <c r="G185">
-        <v>0.4395898367074212</v>
+        <v>0.5950136947599719</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -4785,19 +4785,19 @@
         <v>2018</v>
       </c>
       <c r="C186">
-        <v>0.196751734251068</v>
+        <v>0.158480890777076</v>
       </c>
       <c r="D186">
-        <v>0.06242271179009584</v>
+        <v>0.04743024839035445</v>
       </c>
       <c r="E186">
-        <v>0.512179870814625</v>
+        <v>0.5573233008488656</v>
       </c>
       <c r="F186">
-        <v>0.4400162483498539</v>
+        <v>0.168488632130429</v>
       </c>
       <c r="G186">
-        <v>0.4240454662179834</v>
+        <v>0.3422691351082769</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -4808,19 +4808,19 @@
         <v>2018</v>
       </c>
       <c r="C187">
-        <v>0.1987203963264969</v>
+        <v>0.1850421778307139</v>
       </c>
       <c r="D187">
-        <v>0.08710216405180904</v>
+        <v>0.1788046988139618</v>
       </c>
       <c r="E187">
-        <v>0.524294399618328</v>
+        <v>0.7444429916989941</v>
       </c>
       <c r="F187">
-        <v>0.4531522724706072</v>
+        <v>0.3743224178839375</v>
       </c>
       <c r="G187">
-        <v>0.4217474334453263</v>
+        <v>0.3090997780467987</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -4831,19 +4831,19 @@
         <v>2018</v>
       </c>
       <c r="C188">
-        <v>0.1952572074352955</v>
+        <v>0.1412933787690386</v>
       </c>
       <c r="D188">
-        <v>0.07860315328818032</v>
+        <v>0.0883775230276328</v>
       </c>
       <c r="E188">
-        <v>0.4839376855251399</v>
+        <v>0.160795923116943</v>
       </c>
       <c r="F188">
-        <v>0.4608381815119467</v>
+        <v>0.5423792217938735</v>
       </c>
       <c r="G188">
-        <v>0.4157530484784426</v>
+        <v>0.2334199848236019</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -4854,19 +4854,19 @@
         <v>2018</v>
       </c>
       <c r="C189">
-        <v>0.2199403762249464</v>
+        <v>0.7029668605328265</v>
       </c>
       <c r="D189">
-        <v>0.1136838537583229</v>
+        <v>0.8658164916301239</v>
       </c>
       <c r="E189">
-        <v>0.4828519675971059</v>
+        <v>0.1529622628698455</v>
       </c>
       <c r="F189">
-        <v>0.4366476251296185</v>
+        <v>0.1374388307709453</v>
       </c>
       <c r="G189">
-        <v>0.451657553128092</v>
+        <v>0.7610139687219184</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -4877,19 +4877,19 @@
         <v>2018</v>
       </c>
       <c r="C190">
-        <v>0.198827434768421</v>
+        <v>0.1866226277651163</v>
       </c>
       <c r="D190">
-        <v>0.1002701210620054</v>
+        <v>0.5390611168971742</v>
       </c>
       <c r="E190">
-        <v>0.5484374656509687</v>
+        <v>0.9111827533765448</v>
       </c>
       <c r="F190">
-        <v>0.500062184649315</v>
+        <v>0.9418006793408307</v>
       </c>
       <c r="G190">
-        <v>0.4155554873543697</v>
+        <v>0.2312118139251591</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -4900,19 +4900,19 @@
         <v>2018</v>
       </c>
       <c r="C191">
-        <v>0.2153943269406828</v>
+        <v>0.585181696163613</v>
       </c>
       <c r="D191">
-        <v>0.09847087832348624</v>
+        <v>0.4785974385305015</v>
       </c>
       <c r="E191">
-        <v>0.4920250085541307</v>
+        <v>0.2372781092775209</v>
       </c>
       <c r="F191">
-        <v>0.451848464271231</v>
+        <v>0.3479776521726393</v>
       </c>
       <c r="G191">
-        <v>0.469790749818933</v>
+        <v>0.8931123973446953</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -4923,19 +4923,19 @@
         <v>2018</v>
       </c>
       <c r="C192">
-        <v>0.2148498172368086</v>
+        <v>0.5699504704624241</v>
       </c>
       <c r="D192">
-        <v>0.1055704056948066</v>
+        <v>0.7038836863701364</v>
       </c>
       <c r="E192">
-        <v>0.4967728561570726</v>
+        <v>0.2984814286428987</v>
       </c>
       <c r="F192">
-        <v>0.4414387024196547</v>
+        <v>0.1840559945404915</v>
       </c>
       <c r="G192">
-        <v>0.4285176512520501</v>
+        <v>0.4120193110938264</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -4946,19 +4946,19 @@
         <v>2018</v>
       </c>
       <c r="C193">
-        <v>0.2137887550237808</v>
+        <v>0.539901863556624</v>
       </c>
       <c r="D193">
-        <v>0.09464878470088736</v>
+        <v>0.3557596835536964</v>
       </c>
       <c r="E193">
-        <v>0.5233199363598523</v>
+        <v>0.7319554914547808</v>
       </c>
       <c r="F193">
-        <v>0.4268189782020751</v>
+        <v>0.08259487383294123</v>
       </c>
       <c r="G193">
-        <v>0.4486173718146841</v>
+        <v>0.725061531803895</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -4969,19 +4969,19 @@
         <v>2018</v>
       </c>
       <c r="C194">
-        <v>0.2001708416348441</v>
+        <v>0.2077136246541649</v>
       </c>
       <c r="D194">
-        <v>0.08431592071750178</v>
+        <v>0.1389013287743272</v>
       </c>
       <c r="E194">
-        <v>0.4923622699064557</v>
+        <v>0.2412194841165668</v>
       </c>
       <c r="F194">
-        <v>0.4564846335966925</v>
+        <v>0.4455574694382664</v>
       </c>
       <c r="G194">
-        <v>0.4492322496492008</v>
+        <v>0.7326820169679568</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -4992,19 +4992,19 @@
         <v>2018</v>
       </c>
       <c r="C195">
-        <v>0.1883482924590122</v>
+        <v>0.08805958052091961</v>
       </c>
       <c r="D195">
-        <v>0.09383086422222421</v>
+        <v>0.3317050580374787</v>
       </c>
       <c r="E195">
-        <v>0.5229586431427787</v>
+        <v>0.7271941128009323</v>
       </c>
       <c r="F195">
-        <v>0.4321679582302416</v>
+        <v>0.1069263561212568</v>
       </c>
       <c r="G195">
-        <v>0.4138696103595448</v>
+        <v>0.2131246473639968</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -5015,19 +5015,19 @@
         <v>2018</v>
       </c>
       <c r="C196">
-        <v>0.2265793487427071</v>
+        <v>0.8293400100009668</v>
       </c>
       <c r="D196">
-        <v>0.0909862146867603</v>
+        <v>0.2568475726470723</v>
       </c>
       <c r="E196">
-        <v>0.4898162869407451</v>
+        <v>0.2130048654267357</v>
       </c>
       <c r="F196">
-        <v>0.4512048817060124</v>
+        <v>0.3353734698789665</v>
       </c>
       <c r="G196">
-        <v>0.4486632157789106</v>
+        <v>0.7256357349776411</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -5038,19 +5038,19 @@
         <v>2018</v>
       </c>
       <c r="C197">
-        <v>0.2161104133495021</v>
+        <v>0.60494648116255</v>
       </c>
       <c r="D197">
-        <v>0.1095366121614666</v>
+        <v>0.7981833419811917</v>
       </c>
       <c r="E197">
-        <v>0.5520021653382002</v>
+        <v>0.9201622721392513</v>
       </c>
       <c r="F197">
-        <v>0.4793089939484813</v>
+        <v>0.8474250805457357</v>
       </c>
       <c r="G197">
-        <v>0.3964796797590929</v>
+        <v>0.09572588646907843</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -5061,19 +5061,19 @@
         <v>2018</v>
       </c>
       <c r="C198">
-        <v>0.2209066650726731</v>
+        <v>0.7250667273570081</v>
       </c>
       <c r="D198">
-        <v>0.1041259803170446</v>
+        <v>0.6624991741233984</v>
       </c>
       <c r="E198">
-        <v>0.4936771797416872</v>
+        <v>0.2571838254623356</v>
       </c>
       <c r="F198">
-        <v>0.419262335405006</v>
+        <v>0.06272167705024595</v>
       </c>
       <c r="G198">
-        <v>0.4739951505426963</v>
+        <v>0.9085030311162983</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -5084,19 +5084,19 @@
         <v>2018</v>
       </c>
       <c r="C199">
-        <v>0.2410295725006534</v>
+        <v>0.9407781862365857</v>
       </c>
       <c r="D199">
-        <v>0.1235095054310393</v>
+        <v>0.9391249253001965</v>
       </c>
       <c r="E199">
-        <v>0.4822132364292356</v>
+        <v>0.1485928706142779</v>
       </c>
       <c r="F199">
-        <v>0.4430705371876625</v>
+        <v>0.2038696371228902</v>
       </c>
       <c r="G199">
-        <v>0.4230482684458319</v>
+        <v>0.3276201037545363</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -5107,19 +5107,19 @@
         <v>2018</v>
       </c>
       <c r="C200">
-        <v>0.2213701917662683</v>
+        <v>0.7352356036456607</v>
       </c>
       <c r="D200">
-        <v>0.08886171550796813</v>
+        <v>0.2107078552079151</v>
       </c>
       <c r="E200">
-        <v>0.5609101013512616</v>
+        <v>0.9346160135795685</v>
       </c>
       <c r="F200">
-        <v>0.4299067413422158</v>
+        <v>0.09528686930632546</v>
       </c>
       <c r="G200">
-        <v>0.425119523977658</v>
+        <v>0.358454291695001</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -5130,19 +5130,19 @@
         <v>2018</v>
       </c>
       <c r="C201">
-        <v>0.2136592104842898</v>
+        <v>0.5362092908644722</v>
       </c>
       <c r="D201">
-        <v>0.102519332862097</v>
+        <v>0.6128772804906198</v>
       </c>
       <c r="E201">
-        <v>0.5318897484774726</v>
+        <v>0.824067500911066</v>
       </c>
       <c r="F201">
-        <v>0.4412266631178535</v>
+        <v>0.1816368144238864</v>
       </c>
       <c r="G201">
-        <v>0.4075323800490314</v>
+        <v>0.1568579261763871</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -5153,19 +5153,19 @@
         <v>2018</v>
       </c>
       <c r="C202">
-        <v>0.2255646832536408</v>
+        <v>0.8138989484883175</v>
       </c>
       <c r="D202">
-        <v>0.1121217211451576</v>
+        <v>0.8437864332592639</v>
       </c>
       <c r="E202">
-        <v>0.4849960238390185</v>
+        <v>0.1689442742991794</v>
       </c>
       <c r="F202">
-        <v>0.4819770724463643</v>
+        <v>0.8701868064051665</v>
       </c>
       <c r="G202">
-        <v>0.4126412287079267</v>
+        <v>0.2007929144642156</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -5176,19 +5176,19 @@
         <v>2018</v>
       </c>
       <c r="C203">
-        <v>0.1988768532729621</v>
+        <v>0.187357204594287</v>
       </c>
       <c r="D203">
-        <v>0.09239416016847991</v>
+        <v>0.2920918951683172</v>
       </c>
       <c r="E203">
-        <v>0.518337290779749</v>
+        <v>0.6603171709505701</v>
       </c>
       <c r="F203">
-        <v>0.4673052074496748</v>
+        <v>0.6773176056545416</v>
       </c>
       <c r="G203">
-        <v>0.406178573754798</v>
+        <v>0.147080177661027</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -5199,19 +5199,19 @@
         <v>2018</v>
       </c>
       <c r="C204">
-        <v>0.2371466271542301</v>
+        <v>0.9252112572707931</v>
       </c>
       <c r="D204">
-        <v>0.1083167221746879</v>
+        <v>0.7723589239540906</v>
       </c>
       <c r="E204">
-        <v>0.4679229727743919</v>
+        <v>0.08659670309077416</v>
       </c>
       <c r="F204">
-        <v>0.4068681881112609</v>
+        <v>0.04894359075345614</v>
       </c>
       <c r="G204">
-        <v>0.4915429295083882</v>
+        <v>0.9420270755776379</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -5222,19 +5222,19 @@
         <v>2018</v>
       </c>
       <c r="C205">
-        <v>0.1941004564615141</v>
+        <v>0.1295882909203797</v>
       </c>
       <c r="D205">
-        <v>0.08885317681945912</v>
+        <v>0.2105394910379833</v>
       </c>
       <c r="E205">
-        <v>0.5366257603080568</v>
+        <v>0.8590996485398724</v>
       </c>
       <c r="F205">
-        <v>0.4599171526039297</v>
+        <v>0.521908591654158</v>
       </c>
       <c r="G205">
-        <v>0.4393530648739619</v>
+        <v>0.591226883672239</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -5245,19 +5245,19 @@
         <v>2021</v>
       </c>
       <c r="C206">
-        <v>0.2312221609442731</v>
+        <v>0.9314244106189963</v>
       </c>
       <c r="D206">
-        <v>0.1193157060778208</v>
+        <v>0.9592599583226403</v>
       </c>
       <c r="E206">
-        <v>0.4243551800319684</v>
+        <v>0.2128085871199779</v>
       </c>
       <c r="F206">
-        <v>0.4540465950167208</v>
+        <v>0.2698698272683144</v>
       </c>
       <c r="G206">
-        <v>0.4493035189359491</v>
+        <v>0.8794398354634292</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -5268,19 +5268,19 @@
         <v>2021</v>
       </c>
       <c r="C207">
-        <v>0.1966528340695517</v>
+        <v>0.3637439968817714</v>
       </c>
       <c r="D207">
-        <v>0.07483028338867559</v>
+        <v>0.07694494231891387</v>
       </c>
       <c r="E207">
-        <v>0.4785499856171764</v>
+        <v>0.9025974546682858</v>
       </c>
       <c r="F207">
-        <v>0.4466456024062592</v>
+        <v>0.2088410293187522</v>
       </c>
       <c r="G207">
-        <v>0.3550114564739476</v>
+        <v>0.0773791173350652</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -5291,19 +5291,19 @@
         <v>2021</v>
       </c>
       <c r="C208">
-        <v>0.2066649482513262</v>
+        <v>0.6349197751298384</v>
       </c>
       <c r="D208">
-        <v>0.09915296415836691</v>
+        <v>0.7469656665010825</v>
       </c>
       <c r="E208">
-        <v>0.4437182196553104</v>
+        <v>0.5203161636368566</v>
       </c>
       <c r="F208">
-        <v>0.4947767773183931</v>
+        <v>0.7293283575588763</v>
       </c>
       <c r="G208">
-        <v>0.4283998334641432</v>
+        <v>0.7270573404701313</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -5314,19 +5314,19 @@
         <v>2021</v>
       </c>
       <c r="C209">
-        <v>0.2349888683754854</v>
+        <v>0.9402770816747671</v>
       </c>
       <c r="D209">
-        <v>0.102021318758718</v>
+        <v>0.8233448502422973</v>
       </c>
       <c r="E209">
-        <v>0.3959656500811977</v>
+        <v>0.0668306249146641</v>
       </c>
       <c r="F209">
-        <v>0.3877930886091536</v>
+        <v>0.05339848553716078</v>
       </c>
       <c r="G209">
-        <v>0.4811992449727103</v>
+        <v>0.9517805876662503</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -5337,19 +5337,19 @@
         <v>2021</v>
       </c>
       <c r="C210">
-        <v>0.17685347648419</v>
+        <v>0.08891538276920202</v>
       </c>
       <c r="D210">
-        <v>0.08431803607497901</v>
+        <v>0.2022103474009374</v>
       </c>
       <c r="E210">
-        <v>0.4237356675311521</v>
+        <v>0.2060616541493318</v>
       </c>
       <c r="F210">
-        <v>0.5286067012245805</v>
+        <v>0.9089129720494977</v>
       </c>
       <c r="G210">
-        <v>0.3927424497435053</v>
+        <v>0.2867882257992822</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -5360,19 +5360,19 @@
         <v>2021</v>
       </c>
       <c r="C211">
-        <v>0.1806810107410171</v>
+        <v>0.1116929437319729</v>
       </c>
       <c r="D211">
-        <v>0.08377658379602157</v>
+        <v>0.1896782901133214</v>
       </c>
       <c r="E211">
-        <v>0.4501580324478033</v>
+        <v>0.634924651721039</v>
       </c>
       <c r="F211">
-        <v>0.4888192656698416</v>
+        <v>0.6698603098745848</v>
       </c>
       <c r="G211">
-        <v>0.3639640407010985</v>
+        <v>0.1006315897659614</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -5383,19 +5383,19 @@
         <v>2021</v>
       </c>
       <c r="C212">
-        <v>0.176919650916797</v>
+        <v>0.08923522462150268</v>
       </c>
       <c r="D212">
-        <v>0.08052766744145834</v>
+        <v>0.1308606346991681</v>
       </c>
       <c r="E212">
-        <v>0.4671469395370388</v>
+        <v>0.8420609707812123</v>
       </c>
       <c r="F212">
-        <v>0.4936295779304531</v>
+        <v>0.7185571252677132</v>
       </c>
       <c r="G212">
-        <v>0.3815389467953125</v>
+        <v>0.188357910069113</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -5406,19 +5406,19 @@
         <v>2021</v>
       </c>
       <c r="C213">
-        <v>0.1870356247460542</v>
+        <v>0.1758199779025608</v>
       </c>
       <c r="D213">
-        <v>0.09458154731164439</v>
+        <v>0.5774561945278178</v>
       </c>
       <c r="E213">
-        <v>0.4439310988783561</v>
+        <v>0.5242448416387738</v>
       </c>
       <c r="F213">
-        <v>0.5007798551644707</v>
+        <v>0.780096524063889</v>
       </c>
       <c r="G213">
-        <v>0.3891005447607909</v>
+        <v>0.2506982509245321</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -5429,19 +5429,19 @@
         <v>2021</v>
       </c>
       <c r="C214">
-        <v>0.2231539464855199</v>
+        <v>0.8939506608757782</v>
       </c>
       <c r="D214">
-        <v>0.09623798705002204</v>
+        <v>0.6444333826838782</v>
       </c>
       <c r="E214">
-        <v>0.4834474154746801</v>
+        <v>0.9169583021907051</v>
       </c>
       <c r="F214">
-        <v>0.4397454480317367</v>
+        <v>0.1645515315859478</v>
       </c>
       <c r="G214">
-        <v>0.4288502667091771</v>
+        <v>0.7316807733902636</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -5452,19 +5452,19 @@
         <v>2021</v>
       </c>
       <c r="C215">
-        <v>0.215115998920525</v>
+        <v>0.8084102629554406</v>
       </c>
       <c r="D215">
-        <v>0.07524146496131558</v>
+        <v>0.07941239997229671</v>
       </c>
       <c r="E215">
-        <v>0.4643818955988884</v>
+        <v>0.8192517558301891</v>
       </c>
       <c r="F215">
-        <v>0.5093096654014533</v>
+        <v>0.8363239484505971</v>
       </c>
       <c r="G215">
-        <v>0.296560357186045</v>
+        <v>0.04009683429231636</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -5475,19 +5475,19 @@
         <v>2021</v>
       </c>
       <c r="C216">
-        <v>0.2065295988168904</v>
+        <v>0.6314557416928173</v>
       </c>
       <c r="D216">
-        <v>0.1145573827280601</v>
+        <v>0.9493551356983521</v>
       </c>
       <c r="E216">
-        <v>0.4053262687769026</v>
+        <v>0.08838912451403658</v>
       </c>
       <c r="F216">
-        <v>0.5708060575954651</v>
+        <v>0.950166176713083</v>
       </c>
       <c r="G216">
-        <v>0.4432801642306603</v>
+        <v>0.8478479025006946</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -5498,19 +5498,19 @@
         <v>2021</v>
       </c>
       <c r="C217">
-        <v>0.2253949013014493</v>
+        <v>0.9078174992588715</v>
       </c>
       <c r="D217">
-        <v>0.104450463316787</v>
+        <v>0.8694641202596425</v>
       </c>
       <c r="E217">
-        <v>0.4001622305299215</v>
+        <v>0.07467540847447446</v>
       </c>
       <c r="F217">
-        <v>0.524381120644448</v>
+        <v>0.8979869907767912</v>
       </c>
       <c r="G217">
-        <v>0.3851580704173176</v>
+        <v>0.2160833153706249</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -5521,19 +5521,19 @@
         <v>2021</v>
       </c>
       <c r="C218">
-        <v>0.1589235128072846</v>
+        <v>0.05166660000482415</v>
       </c>
       <c r="D218">
-        <v>0.07431817149055978</v>
+        <v>0.07409485242595171</v>
       </c>
       <c r="E218">
-        <v>0.4771128630376831</v>
+        <v>0.8973247000913046</v>
       </c>
       <c r="F218">
-        <v>0.4763920064807013</v>
+        <v>0.5240259320976546</v>
       </c>
       <c r="G218">
-        <v>0.361745685725205</v>
+        <v>0.0938655411157171</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -5544,19 +5544,19 @@
         <v>2021</v>
       </c>
       <c r="C219">
-        <v>0.2073141357611993</v>
+        <v>0.6512920657187788</v>
       </c>
       <c r="D219">
-        <v>0.09132733394054382</v>
+        <v>0.4396078673868273</v>
       </c>
       <c r="E219">
-        <v>0.4654103776872052</v>
+        <v>0.8281862885156275</v>
       </c>
       <c r="F219">
-        <v>0.4553578950092508</v>
+        <v>0.2821734409082832</v>
       </c>
       <c r="G219">
-        <v>0.4220026697930813</v>
+        <v>0.6553630812380201</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -5567,19 +5567,19 @@
         <v>2021</v>
       </c>
       <c r="C220">
-        <v>0.1872410893139634</v>
+        <v>0.1786030988478238</v>
       </c>
       <c r="D220">
-        <v>0.0890295061343087</v>
+        <v>0.3479444776753357</v>
       </c>
       <c r="E220">
-        <v>0.4340837934356651</v>
+        <v>0.3477958160068784</v>
       </c>
       <c r="F220">
-        <v>0.5157856414396822</v>
+        <v>0.8678875180341302</v>
       </c>
       <c r="G220">
-        <v>0.3714963494895176</v>
+        <v>0.1298959294816566</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -5590,19 +5590,19 @@
         <v>2021</v>
       </c>
       <c r="C221">
-        <v>0.1912280863953741</v>
+        <v>0.2431424868872981</v>
       </c>
       <c r="D221">
-        <v>0.08138747279580463</v>
+        <v>0.1439137568531159</v>
       </c>
       <c r="E221">
-        <v>0.4218002293825827</v>
+        <v>0.1863956139809727</v>
       </c>
       <c r="F221">
-        <v>0.4700081882253128</v>
+        <v>0.4449522787236815</v>
       </c>
       <c r="G221">
-        <v>0.4088037732588596</v>
+        <v>0.4837200459813916</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -5613,19 +5613,19 @@
         <v>2021</v>
       </c>
       <c r="C222">
-        <v>0.1781926771600889</v>
+        <v>0.09585393908069123</v>
       </c>
       <c r="D222">
-        <v>0.08373186894162542</v>
+        <v>0.1886809967696211</v>
       </c>
       <c r="E222">
-        <v>0.4591954884748464</v>
+        <v>0.7653701227642169</v>
       </c>
       <c r="F222">
-        <v>0.4923285031744823</v>
+        <v>0.7059379982640765</v>
       </c>
       <c r="G222">
-        <v>0.4708238890855749</v>
+        <v>0.9395568641140779</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -5636,19 +5636,19 @@
         <v>2021</v>
       </c>
       <c r="C223">
-        <v>0.2020998911854409</v>
+        <v>0.5113896194412392</v>
       </c>
       <c r="D223">
-        <v>0.0986757601762725</v>
+        <v>0.7318168741991591</v>
       </c>
       <c r="E223">
-        <v>0.4522993406881193</v>
+        <v>0.669764685623179</v>
       </c>
       <c r="F223">
-        <v>0.4468921488342298</v>
+        <v>0.2106433475319135</v>
       </c>
       <c r="G223">
-        <v>0.419025181662706</v>
+        <v>0.6186414427370149</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -5659,19 +5659,19 @@
         <v>2021</v>
       </c>
       <c r="C224">
-        <v>0.2228550107527709</v>
+        <v>0.8918396411600211</v>
       </c>
       <c r="D224">
-        <v>0.1023525281033077</v>
+        <v>0.8305753933782656</v>
       </c>
       <c r="E224">
-        <v>0.4288502841564162</v>
+        <v>0.26851189329506</v>
       </c>
       <c r="F224">
-        <v>0.4666909734351871</v>
+        <v>0.4048749041594162</v>
       </c>
       <c r="G224">
-        <v>0.4288472570708934</v>
+        <v>0.7316500780716189</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -5682,19 +5682,19 @@
         <v>2021</v>
       </c>
       <c r="C225">
-        <v>0.2196406502869104</v>
+        <v>0.8645214882350141</v>
       </c>
       <c r="D225">
-        <v>0.09660713237452385</v>
+        <v>0.658640455582723</v>
       </c>
       <c r="E225">
-        <v>0.3834378845251049</v>
+        <v>0.05410400862002438</v>
       </c>
       <c r="F225">
-        <v>0.4328666026431401</v>
+        <v>0.1311178131899851</v>
       </c>
       <c r="G225">
-        <v>0.4081432054574997</v>
+        <v>0.4748765273554038</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -5705,19 +5705,19 @@
         <v>2021</v>
       </c>
       <c r="C226">
-        <v>0.2057821694787881</v>
+        <v>0.6120372638379006</v>
       </c>
       <c r="D226">
-        <v>0.08459744276102531</v>
+        <v>0.2090116448980626</v>
       </c>
       <c r="E226">
-        <v>0.4555091352866041</v>
+        <v>0.717618884514324</v>
       </c>
       <c r="F226">
-        <v>0.4367832686837996</v>
+        <v>0.1489512326141105</v>
       </c>
       <c r="G226">
-        <v>0.5177460464812714</v>
+        <v>0.9658585594588524</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -5728,19 +5728,19 @@
         <v>2021</v>
       </c>
       <c r="C227">
-        <v>0.1941157091650169</v>
+        <v>0.3028779720093029</v>
       </c>
       <c r="D227">
-        <v>0.08765761847864073</v>
+        <v>0.2988591000607092</v>
       </c>
       <c r="E227">
-        <v>0.4417146608873033</v>
+        <v>0.4832443967910078</v>
       </c>
       <c r="F227">
-        <v>0.508243231551798</v>
+        <v>0.830259035845595</v>
       </c>
       <c r="G227">
-        <v>0.3541908234164467</v>
+        <v>0.07572773713102482</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -5751,19 +5751,19 @@
         <v>2021</v>
       </c>
       <c r="C228">
-        <v>0.174372243308618</v>
+        <v>0.07844398240701028</v>
       </c>
       <c r="D228">
-        <v>0.08893332534540699</v>
+        <v>0.3443442946107983</v>
       </c>
       <c r="E228">
-        <v>0.4468382734026219</v>
+        <v>0.5772229423008101</v>
       </c>
       <c r="F228">
-        <v>0.5715809129054167</v>
+        <v>0.9503698925152489</v>
       </c>
       <c r="G228">
-        <v>0.3651308549173779</v>
+        <v>0.1044987316100381</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -5774,19 +5774,19 @@
         <v>2021</v>
       </c>
       <c r="C229">
-        <v>0.1809075520699083</v>
+        <v>0.1133508665542448</v>
       </c>
       <c r="D229">
-        <v>0.08399351663594369</v>
+        <v>0.1945976608614571</v>
       </c>
       <c r="E229">
-        <v>0.4349035605515871</v>
+        <v>0.3614510164922013</v>
       </c>
       <c r="F229">
-        <v>0.488760151997041</v>
+        <v>0.6692283004825401</v>
       </c>
       <c r="G229">
-        <v>0.4185363092470371</v>
+        <v>0.6124478643289263</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -5797,19 +5797,19 @@
         <v>2021</v>
       </c>
       <c r="C230">
-        <v>0.1806484754426529</v>
+        <v>0.111458021309075</v>
       </c>
       <c r="D230">
-        <v>0.09273681487315211</v>
+        <v>0.4992633523471841</v>
       </c>
       <c r="E230">
-        <v>0.4849170913069824</v>
+        <v>0.920354133308912</v>
       </c>
       <c r="F230">
-        <v>0.545248589281418</v>
+        <v>0.9355245894131596</v>
       </c>
       <c r="G230">
-        <v>0.376859409254606</v>
+        <v>0.1579526887205009</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -5820,19 +5820,19 @@
         <v>2021</v>
       </c>
       <c r="C231">
-        <v>0.2505861762215593</v>
+        <v>0.9536372928410434</v>
       </c>
       <c r="D231">
-        <v>0.1272594974955857</v>
+        <v>0.9648836047639991</v>
       </c>
       <c r="E231">
-        <v>0.3821751020485755</v>
+        <v>0.0533935538047833</v>
       </c>
       <c r="F231">
-        <v>0.4153018191445689</v>
+        <v>0.0808327906520615</v>
       </c>
       <c r="G231">
-        <v>0.4087476872790871</v>
+        <v>0.482968473916755</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -5843,19 +5843,19 @@
         <v>2021</v>
       </c>
       <c r="C232">
-        <v>0.2066735672270646</v>
+        <v>0.6351397907791176</v>
       </c>
       <c r="D232">
-        <v>0.09442873564666694</v>
+        <v>0.5710706737096817</v>
       </c>
       <c r="E232">
-        <v>0.4454994522762009</v>
+        <v>0.5530187168751058</v>
       </c>
       <c r="F232">
-        <v>0.4673522314508276</v>
+        <v>0.4127623465007456</v>
       </c>
       <c r="G232">
-        <v>0.3885855092285097</v>
+        <v>0.2459117576245188</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -5866,19 +5866,19 @@
         <v>2021</v>
       </c>
       <c r="C233">
-        <v>0.2032106635505584</v>
+        <v>0.5423221931934236</v>
       </c>
       <c r="D233">
-        <v>0.09943608651961576</v>
+        <v>0.7556265625020144</v>
       </c>
       <c r="E233">
-        <v>0.4803777436109643</v>
+        <v>0.9085629193093656</v>
       </c>
       <c r="F233">
-        <v>0.4381266434747538</v>
+        <v>0.1557888856973191</v>
       </c>
       <c r="G233">
-        <v>0.4121608407221335</v>
+        <v>0.5287725335491107</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -5889,19 +5889,19 @@
         <v>2021</v>
       </c>
       <c r="C234">
-        <v>0.1981220438686414</v>
+        <v>0.4019199969095645</v>
       </c>
       <c r="D234">
-        <v>0.08725951691855388</v>
+        <v>0.2855867513242728</v>
       </c>
       <c r="E234">
-        <v>0.4505249016110922</v>
+        <v>0.6410428687577508</v>
       </c>
       <c r="F234">
-        <v>0.4775405022732445</v>
+        <v>0.5382371380429971</v>
       </c>
       <c r="G234">
-        <v>0.3965397002726981</v>
+        <v>0.3284306689162153</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -5912,19 +5912,19 @@
         <v>2021</v>
       </c>
       <c r="C235">
-        <v>0.2146157294905293</v>
+        <v>0.8007093865614403</v>
       </c>
       <c r="D235">
-        <v>0.1019191756319185</v>
+        <v>0.8210511267163613</v>
       </c>
       <c r="E235">
-        <v>0.4346789683651055</v>
+        <v>0.3576808706115488</v>
       </c>
       <c r="F235">
-        <v>0.4759024289434906</v>
+        <v>0.517951990330951</v>
       </c>
       <c r="G235">
-        <v>0.3754658857926689</v>
+        <v>0.1500046437303666</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -5935,19 +5935,19 @@
         <v>2021</v>
       </c>
       <c r="C236">
-        <v>0.2018053838821608</v>
+        <v>0.5031615881124758</v>
       </c>
       <c r="D236">
-        <v>0.09130984702136526</v>
+        <v>0.4388780132975387</v>
       </c>
       <c r="E236">
-        <v>0.4672377950083594</v>
+        <v>0.8427465401656959</v>
       </c>
       <c r="F236">
-        <v>0.4856059794356953</v>
+        <v>0.6344452928062276</v>
       </c>
       <c r="G236">
-        <v>0.4293750023884053</v>
+        <v>0.7369918469503343</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -5958,19 +5958,19 @@
         <v>2021</v>
       </c>
       <c r="C237">
-        <v>0.1866472860464024</v>
+        <v>0.1706965226601481</v>
       </c>
       <c r="D237">
-        <v>0.07485701118504974</v>
+        <v>0.07710035013181743</v>
       </c>
       <c r="E237">
-        <v>0.4376436046059937</v>
+        <v>0.408998040279583</v>
       </c>
       <c r="F237">
-        <v>0.5123382671015844</v>
+        <v>0.8521676163653058</v>
       </c>
       <c r="G237">
-        <v>0.4019250706247048</v>
+        <v>0.3935676408499774</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -5981,19 +5981,19 @@
         <v>2021</v>
       </c>
       <c r="C238">
-        <v>0.208637078242152</v>
+        <v>0.6832948767083462</v>
       </c>
       <c r="D238">
-        <v>0.09702852575115566</v>
+        <v>0.6744679462097727</v>
       </c>
       <c r="E238">
-        <v>0.4448463207466827</v>
+        <v>0.5410792595876375</v>
       </c>
       <c r="F238">
-        <v>0.3849245582564586</v>
+        <v>0.05218901059889932</v>
       </c>
       <c r="G238">
-        <v>0.3745295356421824</v>
+        <v>0.1449317625715594</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -6004,19 +6004,19 @@
         <v>2021</v>
       </c>
       <c r="C239">
-        <v>0.1885600274512246</v>
+        <v>0.1976973781073973</v>
       </c>
       <c r="D239">
-        <v>0.09448672533321546</v>
+        <v>0.5734969601116104</v>
       </c>
       <c r="E239">
-        <v>0.4256600840030539</v>
+        <v>0.2277524906801136</v>
       </c>
       <c r="F239">
-        <v>0.5234867511149316</v>
+        <v>0.8953811225376505</v>
       </c>
       <c r="G239">
-        <v>0.4310786802937543</v>
+        <v>0.753671523375902</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -6027,19 +6027,19 @@
         <v>2021</v>
       </c>
       <c r="C240">
-        <v>0.2173471025292532</v>
+        <v>0.8389859237814263</v>
       </c>
       <c r="D240">
-        <v>0.09794739320429358</v>
+        <v>0.707394604661733</v>
       </c>
       <c r="E240">
-        <v>0.421751170938662</v>
+        <v>0.1859244133648875</v>
       </c>
       <c r="F240">
-        <v>0.4793258684630145</v>
+        <v>0.560169537310851</v>
       </c>
       <c r="G240">
-        <v>0.3993363366377963</v>
+        <v>0.3614646064630647</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -6050,19 +6050,19 @@
         <v>2021</v>
       </c>
       <c r="C241">
-        <v>0.2104333124581115</v>
+        <v>0.7234575943596376</v>
       </c>
       <c r="D241">
-        <v>0.09035068918382734</v>
+        <v>0.3994819157901973</v>
       </c>
       <c r="E241">
-        <v>0.4823484623921314</v>
+        <v>0.9141671559461519</v>
       </c>
       <c r="F241">
-        <v>0.4490175562054295</v>
+        <v>0.2268355810614089</v>
       </c>
       <c r="G241">
-        <v>0.4122690036472563</v>
+        <v>0.5302213222030868</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -6073,19 +6073,19 @@
         <v>2021</v>
       </c>
       <c r="C242">
-        <v>0.2062938014683181</v>
+        <v>0.6253813958950809</v>
       </c>
       <c r="D242">
-        <v>0.09605338815748692</v>
+        <v>0.6372168493881999</v>
       </c>
       <c r="E242">
-        <v>0.4069720953978495</v>
+        <v>0.09396905049770632</v>
       </c>
       <c r="F242">
-        <v>0.4762406851995645</v>
+        <v>0.5221493833094555</v>
       </c>
       <c r="G242">
-        <v>0.4484060355624737</v>
+        <v>0.8752698264251587</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -6096,19 +6096,19 @@
         <v>2021</v>
       </c>
       <c r="C243">
-        <v>0.2333288767341528</v>
+        <v>0.9368351955922155</v>
       </c>
       <c r="D243">
-        <v>0.1141191450171766</v>
+        <v>0.9479698448009155</v>
       </c>
       <c r="E243">
-        <v>0.4011066556919933</v>
+        <v>0.07680817614708058</v>
       </c>
       <c r="F243">
-        <v>0.4168560056347391</v>
+        <v>0.08379009822474709</v>
       </c>
       <c r="G243">
-        <v>0.4093876917047526</v>
+        <v>0.4915508198555852</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -6119,19 +6119,19 @@
         <v>2021</v>
       </c>
       <c r="C244">
-        <v>0.1912411867367253</v>
+        <v>0.2433887963461854</v>
       </c>
       <c r="D244">
-        <v>0.07589727308734256</v>
+        <v>0.08370600133715755</v>
       </c>
       <c r="E244">
-        <v>0.4683795423093178</v>
+        <v>0.851033990980782</v>
       </c>
       <c r="F244">
-        <v>0.4105898689634254</v>
+        <v>0.0731246430030877</v>
       </c>
       <c r="G244">
-        <v>0.4554138679630184</v>
+        <v>0.9035079067397014</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -6142,19 +6142,19 @@
         <v>2021</v>
       </c>
       <c r="C245">
-        <v>0.1781305787712048</v>
+        <v>0.09550965131733158</v>
       </c>
       <c r="D245">
-        <v>0.07485782550681441</v>
+        <v>0.07710509563753705</v>
       </c>
       <c r="E245">
-        <v>0.4127554451105927</v>
+        <v>0.1196968000642881</v>
       </c>
       <c r="F245">
-        <v>0.4798851857395224</v>
+        <v>0.5669869395113736</v>
       </c>
       <c r="G245">
-        <v>0.4870801923084987</v>
+        <v>0.9562512154946463</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -6165,19 +6165,19 @@
         <v>2021</v>
       </c>
       <c r="C246">
-        <v>0.1865559036032368</v>
+        <v>0.1695165920486879</v>
       </c>
       <c r="D246">
-        <v>0.08000912569365787</v>
+        <v>0.1237545839739815</v>
       </c>
       <c r="E246">
-        <v>0.4616892754117585</v>
+        <v>0.7931738596787061</v>
       </c>
       <c r="F246">
-        <v>0.448874398886568</v>
+        <v>0.2257078711136461</v>
       </c>
       <c r="G246">
-        <v>0.4357905119324429</v>
+        <v>0.7952387020822782</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -6188,19 +6188,19 @@
         <v>2021</v>
       </c>
       <c r="C247">
-        <v>0.2045063295727896</v>
+        <v>0.5779106426147825</v>
       </c>
       <c r="D247">
-        <v>0.09561763390817062</v>
+        <v>0.6199087170192592</v>
       </c>
       <c r="E247">
-        <v>0.4246109828433464</v>
+        <v>0.2156594943537082</v>
       </c>
       <c r="F247">
-        <v>0.4530980769559803</v>
+        <v>0.2612462316018762</v>
       </c>
       <c r="G247">
-        <v>0.411512236042942</v>
+        <v>0.5200761681749018</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -6211,19 +6211,19 @@
         <v>2021</v>
       </c>
       <c r="C248">
-        <v>0.2022724678657485</v>
+        <v>0.5162085951542217</v>
       </c>
       <c r="D248">
-        <v>0.08432138161789812</v>
+        <v>0.2022904262223906</v>
       </c>
       <c r="E248">
-        <v>0.4834771544540943</v>
+        <v>0.9170307393067008</v>
       </c>
       <c r="F248">
-        <v>0.4328354195971741</v>
+        <v>0.1309877060794147</v>
       </c>
       <c r="G248">
-        <v>0.3775630173205203</v>
+        <v>0.1621521409355089</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -6234,19 +6234,19 @@
         <v>2021</v>
       </c>
       <c r="C249">
-        <v>0.2191467153384312</v>
+        <v>0.8594870292120772</v>
       </c>
       <c r="D249">
-        <v>0.1109343470553003</v>
+        <v>0.9341330591250763</v>
       </c>
       <c r="E249">
-        <v>0.4182764104547944</v>
+        <v>0.1558056739350658</v>
       </c>
       <c r="F249">
-        <v>0.5006269300154882</v>
+        <v>0.7789207225491755</v>
       </c>
       <c r="G249">
-        <v>0.4283097597000662</v>
+        <v>0.726125692369081</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -6257,19 +6257,19 @@
         <v>2021</v>
       </c>
       <c r="C250">
-        <v>0.2278473539546414</v>
+        <v>0.9196108029195667</v>
       </c>
       <c r="D250">
-        <v>0.1253900543146216</v>
+        <v>0.9641995866885225</v>
       </c>
       <c r="E250">
-        <v>0.4180024915826704</v>
+        <v>0.1536925714137724</v>
       </c>
       <c r="F250">
-        <v>0.5188847095649809</v>
+        <v>0.8801199106125367</v>
       </c>
       <c r="G250">
-        <v>0.3926855353513413</v>
+        <v>0.2861944615447877</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -6280,19 +6280,19 @@
         <v>2021</v>
       </c>
       <c r="C251">
-        <v>0.2109334478775094</v>
+        <v>0.7339138603429728</v>
       </c>
       <c r="D251">
-        <v>0.09106166793578088</v>
+        <v>0.4285595029340318</v>
       </c>
       <c r="E251">
-        <v>0.4649585702052671</v>
+        <v>0.8243288830630198</v>
       </c>
       <c r="F251">
-        <v>0.4224786338081229</v>
+        <v>0.09654816772469293</v>
       </c>
       <c r="G251">
-        <v>0.4372850867058686</v>
+        <v>0.8070260690253011</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -6303,19 +6303,19 @@
         <v>2021</v>
       </c>
       <c r="C252">
-        <v>0.2025254326204823</v>
+        <v>0.5232661903034808</v>
       </c>
       <c r="D252">
-        <v>0.09583191391698742</v>
+        <v>0.6284661316159572</v>
       </c>
       <c r="E252">
-        <v>0.4700325243297264</v>
+        <v>0.8620024654571048</v>
       </c>
       <c r="F252">
-        <v>0.4335782721876394</v>
+        <v>0.1341363633256955</v>
       </c>
       <c r="G252">
-        <v>0.4686569884867766</v>
+        <v>0.9360497489003902</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -6326,19 +6326,19 @@
         <v>2021</v>
       </c>
       <c r="C253">
-        <v>0.1961933374948444</v>
+        <v>0.3522057443675366</v>
       </c>
       <c r="D253">
-        <v>0.09480838046375002</v>
+        <v>0.5868835101480543</v>
       </c>
       <c r="E253">
-        <v>0.4317467092623563</v>
+        <v>0.3106005148450121</v>
       </c>
       <c r="F253">
-        <v>0.5247034335453353</v>
+        <v>0.8988995817469352</v>
       </c>
       <c r="G253">
-        <v>0.3554221563856051</v>
+        <v>0.07823187145273046</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -6349,19 +6349,19 @@
         <v>2021</v>
       </c>
       <c r="C254">
-        <v>0.1726795642767821</v>
+        <v>0.07277409079029573</v>
       </c>
       <c r="D254">
-        <v>0.07131063576558107</v>
+        <v>0.06144835012967163</v>
       </c>
       <c r="E254">
-        <v>0.4858656057909259</v>
+        <v>0.9223570361157131</v>
       </c>
       <c r="F254">
-        <v>0.5019048765234412</v>
+        <v>0.7885591790385893</v>
       </c>
       <c r="G254">
-        <v>0.3967746553140091</v>
+        <v>0.3311330874264572</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -6372,19 +6372,19 @@
         <v>2021</v>
       </c>
       <c r="C255">
-        <v>0.227044321710744</v>
+        <v>0.9160903182784629</v>
       </c>
       <c r="D255">
-        <v>0.1155981262857809</v>
+        <v>0.9522590870720786</v>
       </c>
       <c r="E255">
-        <v>0.400658283967706</v>
+        <v>0.07577689407788291</v>
       </c>
       <c r="F255">
-        <v>0.4093148062728746</v>
+        <v>0.07132821456228625</v>
       </c>
       <c r="G255">
-        <v>0.5257372092231566</v>
+        <v>0.9665806762052791</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -6395,19 +6395,19 @@
         <v>2021</v>
       </c>
       <c r="C256">
-        <v>0.1868754661280516</v>
+        <v>0.1736854177900742</v>
       </c>
       <c r="D256">
-        <v>0.09169107412536613</v>
+        <v>0.4548632538252368</v>
       </c>
       <c r="E256">
-        <v>0.4593631804270801</v>
+        <v>0.767353072977407</v>
       </c>
       <c r="F256">
-        <v>0.513437688963352</v>
+        <v>0.857437496075102</v>
       </c>
       <c r="G256">
-        <v>0.3955271869569719</v>
+        <v>0.3169470994402578</v>
       </c>
     </row>
   </sheetData>
